--- a/research/traditional_assets/database/data/qatar/qatar_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_telecom_wireless.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07754281945900368</v>
+        <v>0.07750577663954467</v>
       </c>
       <c r="C2">
-        <v>2384.402560552365</v>
+        <v>2361.677871139335</v>
       </c>
       <c r="D2">
-        <v>2340.402560552365</v>
+        <v>2341.459871139336</v>
       </c>
       <c r="E2">
-        <v>-253.4</v>
+        <v>-229.618</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>23.782</v>
       </c>
       <c r="G2">
         <v>44</v>
@@ -1457,28 +1457,28 @@
         <v>132.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.1962346</v>
       </c>
       <c r="N2">
-        <v>132.5</v>
+        <v>131.3037654</v>
       </c>
       <c r="O2">
-        <v>13.25</v>
+        <v>13.13037654</v>
       </c>
       <c r="P2">
-        <v>119.25</v>
+        <v>118.17338886</v>
       </c>
       <c r="Q2">
-        <v>297.65</v>
+        <v>296.57338886</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07754281945900368</v>
+        <v>0.07783139054499461</v>
       </c>
       <c r="T2">
-        <v>0.6362422799549506</v>
+        <v>0.6420263006818138</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>110.764226348243</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07750577663954467</v>
+        <v>0.07746873382008566</v>
       </c>
       <c r="C3">
-        <v>2361.677871139335</v>
+        <v>2338.954137468668</v>
       </c>
       <c r="D3">
-        <v>2341.459871139336</v>
+        <v>2342.518137468668</v>
       </c>
       <c r="E3">
-        <v>-229.618</v>
+        <v>-205.836</v>
       </c>
       <c r="F3">
-        <v>23.782</v>
+        <v>47.56400000000001</v>
       </c>
       <c r="G3">
         <v>44</v>
@@ -1539,28 +1539,28 @@
         <v>132.5</v>
       </c>
       <c r="M3">
-        <v>1.1962346</v>
+        <v>2.3924692</v>
       </c>
       <c r="N3">
-        <v>131.3037654</v>
+        <v>130.1075308</v>
       </c>
       <c r="O3">
-        <v>13.13037654</v>
+        <v>13.01075308</v>
       </c>
       <c r="P3">
-        <v>118.17338886</v>
+        <v>117.09677772</v>
       </c>
       <c r="Q3">
-        <v>296.57338886</v>
+        <v>295.49677772</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07783139054499461</v>
+        <v>0.07812585083682211</v>
       </c>
       <c r="T3">
-        <v>0.6420263006818138</v>
+        <v>0.6479283626480008</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>110.764226348243</v>
+        <v>55.38211317412151</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07746873382008566</v>
+        <v>0.07743169100062666</v>
       </c>
       <c r="C4">
-        <v>2338.954137468668</v>
+        <v>2316.231360836845</v>
       </c>
       <c r="D4">
-        <v>2342.518137468668</v>
+        <v>2343.577360836845</v>
       </c>
       <c r="E4">
-        <v>-205.836</v>
+        <v>-182.054</v>
       </c>
       <c r="F4">
-        <v>47.56400000000001</v>
+        <v>71.346</v>
       </c>
       <c r="G4">
         <v>44</v>
@@ -1621,28 +1621,28 @@
         <v>132.5</v>
       </c>
       <c r="M4">
-        <v>2.3924692</v>
+        <v>3.5887038</v>
       </c>
       <c r="N4">
-        <v>130.1075308</v>
+        <v>128.9112962</v>
       </c>
       <c r="O4">
-        <v>13.01075308</v>
+        <v>12.89112962</v>
       </c>
       <c r="P4">
-        <v>117.09677772</v>
+        <v>116.02016658</v>
       </c>
       <c r="Q4">
-        <v>295.49677772</v>
+        <v>294.42016658</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07812585083682211</v>
+        <v>0.07842638247487285</v>
       </c>
       <c r="T4">
-        <v>0.6479283626480008</v>
+        <v>0.6539521166134904</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>55.38211317412151</v>
+        <v>36.92140878274768</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07743169100062666</v>
+        <v>0.07739464818116766</v>
       </c>
       <c r="C5">
-        <v>2316.231360836845</v>
+        <v>2293.509542542695</v>
       </c>
       <c r="D5">
-        <v>2343.577360836845</v>
+        <v>2344.637542542695</v>
       </c>
       <c r="E5">
-        <v>-182.054</v>
+        <v>-158.272</v>
       </c>
       <c r="F5">
-        <v>71.346</v>
+        <v>95.12800000000001</v>
       </c>
       <c r="G5">
         <v>44</v>
@@ -1703,28 +1703,28 @@
         <v>132.5</v>
       </c>
       <c r="M5">
-        <v>3.5887038</v>
+        <v>4.784938400000001</v>
       </c>
       <c r="N5">
-        <v>128.9112962</v>
+        <v>127.7150616</v>
       </c>
       <c r="O5">
-        <v>12.89112962</v>
+        <v>12.77150616</v>
       </c>
       <c r="P5">
-        <v>116.02016658</v>
+        <v>114.94355544</v>
       </c>
       <c r="Q5">
-        <v>294.42016658</v>
+        <v>293.34355544</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07842638247487285</v>
+        <v>0.07873317518871631</v>
       </c>
       <c r="T5">
-        <v>0.6539521166134904</v>
+        <v>0.6601013654532614</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>36.92140878274768</v>
+        <v>27.69105658706076</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07739464818116766</v>
+        <v>0.07735760536170865</v>
       </c>
       <c r="C6">
-        <v>2293.509542542695</v>
+        <v>2270.788683887398</v>
       </c>
       <c r="D6">
-        <v>2344.637542542695</v>
+        <v>2345.698683887398</v>
       </c>
       <c r="E6">
-        <v>-158.272</v>
+        <v>-134.49</v>
       </c>
       <c r="F6">
-        <v>95.12800000000001</v>
+        <v>118.91</v>
       </c>
       <c r="G6">
         <v>44</v>
@@ -1785,28 +1785,28 @@
         <v>132.5</v>
       </c>
       <c r="M6">
-        <v>4.784938400000001</v>
+        <v>5.981173000000001</v>
       </c>
       <c r="N6">
-        <v>127.7150616</v>
+        <v>126.518827</v>
       </c>
       <c r="O6">
-        <v>12.77150616</v>
+        <v>12.6518827</v>
       </c>
       <c r="P6">
-        <v>114.94355544</v>
+        <v>113.8669443</v>
       </c>
       <c r="Q6">
-        <v>293.34355544</v>
+        <v>292.2669443</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07873317518871631</v>
+        <v>0.07904642669653542</v>
       </c>
       <c r="T6">
-        <v>0.6601013654532614</v>
+        <v>0.6663800721633429</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>27.69105658706076</v>
+        <v>22.1528452696486</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07735760536170865</v>
+        <v>0.07732056254224964</v>
       </c>
       <c r="C7">
-        <v>2270.788683887398</v>
+        <v>2248.06878617449</v>
       </c>
       <c r="D7">
-        <v>2345.698683887398</v>
+        <v>2346.76078617449</v>
       </c>
       <c r="E7">
-        <v>-134.49</v>
+        <v>-110.708</v>
       </c>
       <c r="F7">
-        <v>118.91</v>
+        <v>142.692</v>
       </c>
       <c r="G7">
         <v>44</v>
@@ -1867,28 +1867,28 @@
         <v>132.5</v>
       </c>
       <c r="M7">
-        <v>5.981173000000001</v>
+        <v>7.177407600000001</v>
       </c>
       <c r="N7">
-        <v>126.518827</v>
+        <v>125.3225924</v>
       </c>
       <c r="O7">
-        <v>12.6518827</v>
+        <v>12.53225924</v>
       </c>
       <c r="P7">
-        <v>113.8669443</v>
+        <v>112.79033316</v>
       </c>
       <c r="Q7">
-        <v>292.2669443</v>
+        <v>291.19033316</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07904642669653542</v>
+        <v>0.07936634313005282</v>
       </c>
       <c r="T7">
-        <v>0.6663800721633429</v>
+        <v>0.6727923683778946</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>22.1528452696486</v>
+        <v>18.46070439137384</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07732056254224964</v>
+        <v>0.07728351972279066</v>
       </c>
       <c r="C8">
-        <v>2248.06878617449</v>
+        <v>2225.349850709871</v>
       </c>
       <c r="D8">
-        <v>2346.76078617449</v>
+        <v>2347.823850709871</v>
       </c>
       <c r="E8">
-        <v>-110.708</v>
+        <v>-86.92600000000002</v>
       </c>
       <c r="F8">
-        <v>142.692</v>
+        <v>166.474</v>
       </c>
       <c r="G8">
         <v>44</v>
@@ -1949,28 +1949,28 @@
         <v>132.5</v>
       </c>
       <c r="M8">
-        <v>7.1774076</v>
+        <v>8.373642199999999</v>
       </c>
       <c r="N8">
-        <v>125.3225924</v>
+        <v>124.1263578</v>
       </c>
       <c r="O8">
-        <v>12.53225924</v>
+        <v>12.41263578</v>
       </c>
       <c r="P8">
-        <v>112.79033316</v>
+        <v>111.71372202</v>
       </c>
       <c r="Q8">
-        <v>291.19033316</v>
+        <v>290.11372202</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07936634313005282</v>
+        <v>0.07969313948687166</v>
       </c>
       <c r="T8">
-        <v>0.6727923683778946</v>
+        <v>0.6793425634357698</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>18.46070439137384</v>
+        <v>15.82346090689186</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07728351972279066</v>
+        <v>0.07724647690333165</v>
       </c>
       <c r="C9">
-        <v>2225.349850709871</v>
+        <v>2202.631878801805</v>
       </c>
       <c r="D9">
-        <v>2347.823850709871</v>
+        <v>2348.887878801805</v>
       </c>
       <c r="E9">
-        <v>-86.92599999999996</v>
+        <v>-63.14399999999998</v>
       </c>
       <c r="F9">
-        <v>166.474</v>
+        <v>190.256</v>
       </c>
       <c r="G9">
         <v>44</v>
@@ -2031,28 +2031,28 @@
         <v>132.5</v>
       </c>
       <c r="M9">
-        <v>8.373642200000003</v>
+        <v>9.569876800000001</v>
       </c>
       <c r="N9">
-        <v>124.1263578</v>
+        <v>122.9301232</v>
       </c>
       <c r="O9">
-        <v>12.41263578</v>
+        <v>12.29301232</v>
       </c>
       <c r="P9">
-        <v>111.71372202</v>
+        <v>110.63711088</v>
       </c>
       <c r="Q9">
-        <v>290.11372202</v>
+        <v>289.03711088</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07969313948687168</v>
+        <v>0.08002704011231701</v>
       </c>
       <c r="T9">
-        <v>0.6793425634357699</v>
+        <v>0.6860351540383816</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>15.82346090689186</v>
+        <v>13.84552829353038</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07724647690333165</v>
+        <v>0.07733093408387265</v>
       </c>
       <c r="C10">
-        <v>2202.631878801805</v>
+        <v>2176.425313438423</v>
       </c>
       <c r="D10">
-        <v>2348.887878801805</v>
+        <v>2346.463313438423</v>
       </c>
       <c r="E10">
-        <v>-63.14399999999998</v>
+        <v>-39.36199999999999</v>
       </c>
       <c r="F10">
-        <v>190.256</v>
+        <v>214.038</v>
       </c>
       <c r="G10">
         <v>44</v>
@@ -2113,45 +2113,45 @@
         <v>132.5</v>
       </c>
       <c r="M10">
-        <v>9.569876800000001</v>
+        <v>11.0871684</v>
       </c>
       <c r="N10">
-        <v>122.9301232</v>
+        <v>121.4128316</v>
       </c>
       <c r="O10">
-        <v>12.29301232</v>
+        <v>12.14128316</v>
       </c>
       <c r="P10">
-        <v>110.63711088</v>
+        <v>109.27154844</v>
       </c>
       <c r="Q10">
-        <v>289.03711088</v>
+        <v>287.67154844</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08002704011231701</v>
+        <v>0.08036827921304686</v>
       </c>
       <c r="T10">
-        <v>0.6860351540383816</v>
+        <v>0.6928748345443473</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.1</v>
       </c>
       <c r="W10">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>13.84552829353038</v>
+        <v>11.95075200625617</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07733093408387265</v>
+        <v>0.07730739126441363</v>
       </c>
       <c r="C11">
-        <v>2176.425313438423</v>
+        <v>2153.318668643442</v>
       </c>
       <c r="D11">
-        <v>2346.463313438423</v>
+        <v>2347.138668643442</v>
       </c>
       <c r="E11">
-        <v>-39.36199999999999</v>
+        <v>-15.57999999999998</v>
       </c>
       <c r="F11">
-        <v>214.038</v>
+        <v>237.82</v>
       </c>
       <c r="G11">
         <v>44</v>
@@ -2195,28 +2195,28 @@
         <v>132.5</v>
       </c>
       <c r="M11">
-        <v>11.0871684</v>
+        <v>12.319076</v>
       </c>
       <c r="N11">
-        <v>121.4128316</v>
+        <v>120.180924</v>
       </c>
       <c r="O11">
-        <v>12.14128316</v>
+        <v>12.0180924</v>
       </c>
       <c r="P11">
-        <v>109.27154844</v>
+        <v>108.1628316</v>
       </c>
       <c r="Q11">
-        <v>287.67154844</v>
+        <v>286.5628316</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08036827921304686</v>
+        <v>0.08071710140490404</v>
       </c>
       <c r="T11">
-        <v>0.6928748345443473</v>
+        <v>0.6998665079504458</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.95075200625617</v>
+        <v>10.75567680563055</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07730739126441363</v>
+        <v>0.07745214844495463</v>
       </c>
       <c r="C12">
-        <v>2153.318668643442</v>
+        <v>2125.390270682319</v>
       </c>
       <c r="D12">
-        <v>2347.138668643442</v>
+        <v>2342.992270682319</v>
       </c>
       <c r="E12">
-        <v>-15.57999999999996</v>
+        <v>8.202000000000027</v>
       </c>
       <c r="F12">
-        <v>237.8200000000001</v>
+        <v>261.602</v>
       </c>
       <c r="G12">
         <v>44</v>
@@ -2277,45 +2277,45 @@
         <v>132.5</v>
       </c>
       <c r="M12">
-        <v>12.319076</v>
+        <v>13.995707</v>
       </c>
       <c r="N12">
-        <v>120.180924</v>
+        <v>118.504293</v>
       </c>
       <c r="O12">
-        <v>12.0180924</v>
+        <v>11.8504293</v>
       </c>
       <c r="P12">
-        <v>108.1628316</v>
+        <v>106.6538637</v>
       </c>
       <c r="Q12">
-        <v>286.5628316</v>
+        <v>285.0538637</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08071710140490404</v>
+        <v>0.08107376229770183</v>
       </c>
       <c r="T12">
-        <v>0.6998665079504458</v>
+        <v>0.7070152976128609</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.1</v>
       </c>
       <c r="W12">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>10.75567680563055</v>
+        <v>9.467188760096219</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07745214844495463</v>
+        <v>0.07744390562549563</v>
       </c>
       <c r="C13">
-        <v>2125.390270682319</v>
+        <v>2101.843983093775</v>
       </c>
       <c r="D13">
-        <v>2342.992270682319</v>
+        <v>2343.227983093775</v>
       </c>
       <c r="E13">
-        <v>8.202000000000027</v>
+        <v>31.98400000000001</v>
       </c>
       <c r="F13">
-        <v>261.602</v>
+        <v>285.384</v>
       </c>
       <c r="G13">
         <v>44</v>
@@ -2359,28 +2359,28 @@
         <v>132.5</v>
       </c>
       <c r="M13">
-        <v>13.995707</v>
+        <v>15.268044</v>
       </c>
       <c r="N13">
-        <v>118.504293</v>
+        <v>117.231956</v>
       </c>
       <c r="O13">
-        <v>11.8504293</v>
+        <v>11.7231956</v>
       </c>
       <c r="P13">
-        <v>106.6538637</v>
+        <v>105.5087604</v>
       </c>
       <c r="Q13">
-        <v>285.0538637</v>
+        <v>283.9087604</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08107376229770183</v>
+        <v>0.08143852911988139</v>
       </c>
       <c r="T13">
-        <v>0.7070152976128609</v>
+        <v>0.7143265597676037</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>9.467188760096219</v>
+        <v>8.678256363421534</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07744390562549563</v>
+        <v>0.07743566280603663</v>
       </c>
       <c r="C14">
-        <v>2101.843983093775</v>
+        <v>2078.297742936828</v>
       </c>
       <c r="D14">
-        <v>2343.227983093775</v>
+        <v>2343.463742936829</v>
       </c>
       <c r="E14">
-        <v>31.98400000000001</v>
+        <v>55.76600000000005</v>
       </c>
       <c r="F14">
-        <v>285.384</v>
+        <v>309.1660000000001</v>
       </c>
       <c r="G14">
         <v>44</v>
@@ -2441,28 +2441,28 @@
         <v>132.5</v>
       </c>
       <c r="M14">
-        <v>15.268044</v>
+        <v>16.540381</v>
       </c>
       <c r="N14">
-        <v>117.231956</v>
+        <v>115.959619</v>
       </c>
       <c r="O14">
-        <v>11.7231956</v>
+        <v>11.5959619</v>
       </c>
       <c r="P14">
-        <v>105.5087604</v>
+        <v>104.3636571</v>
       </c>
       <c r="Q14">
-        <v>283.9087604</v>
+        <v>282.7636571</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08143852911988139</v>
+        <v>0.081811681386249</v>
       </c>
       <c r="T14">
-        <v>0.7143265597676037</v>
+        <v>0.7218058969144094</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.678256363421534</v>
+        <v>8.010698181619876</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07743566280603663</v>
+        <v>0.07752821998657761</v>
       </c>
       <c r="C15">
-        <v>2078.297742936828</v>
+        <v>2051.871158237363</v>
       </c>
       <c r="D15">
-        <v>2343.463742936829</v>
+        <v>2340.819158237362</v>
       </c>
       <c r="E15">
-        <v>55.76600000000005</v>
+        <v>79.54800000000009</v>
       </c>
       <c r="F15">
-        <v>309.1660000000001</v>
+        <v>332.9480000000001</v>
       </c>
       <c r="G15">
         <v>44</v>
@@ -2523,45 +2523,45 @@
         <v>132.5</v>
       </c>
       <c r="M15">
-        <v>16.540381</v>
+        <v>18.07907640000001</v>
       </c>
       <c r="N15">
-        <v>115.959619</v>
+        <v>114.4209236</v>
       </c>
       <c r="O15">
-        <v>11.5959619</v>
+        <v>11.44209236</v>
       </c>
       <c r="P15">
-        <v>104.3636571</v>
+        <v>102.97883124</v>
       </c>
       <c r="Q15">
-        <v>282.7636571</v>
+        <v>281.37883124</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.081811681386249</v>
+        <v>0.08219351161229956</v>
       </c>
       <c r="T15">
-        <v>0.7218058969144094</v>
+        <v>0.7294591721343968</v>
       </c>
       <c r="U15">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.1</v>
       </c>
       <c r="W15">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y15">
-        <v>8.010698181619876</v>
+        <v>7.328914213781404</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07752821998657761</v>
+        <v>0.07752717716711863</v>
       </c>
       <c r="C16">
-        <v>2051.871158237363</v>
+        <v>2028.118920890096</v>
       </c>
       <c r="D16">
-        <v>2340.819158237362</v>
+        <v>2340.848920890096</v>
       </c>
       <c r="E16">
-        <v>79.54800000000009</v>
+        <v>103.3300000000001</v>
       </c>
       <c r="F16">
-        <v>332.9480000000001</v>
+        <v>356.7300000000001</v>
       </c>
       <c r="G16">
         <v>44</v>
@@ -2605,28 +2605,28 @@
         <v>132.5</v>
       </c>
       <c r="M16">
-        <v>18.07907640000001</v>
+        <v>19.370439</v>
       </c>
       <c r="N16">
-        <v>114.4209236</v>
+        <v>113.129561</v>
       </c>
       <c r="O16">
-        <v>11.44209236</v>
+        <v>11.3129561</v>
       </c>
       <c r="P16">
-        <v>102.97883124</v>
+        <v>101.8166049</v>
       </c>
       <c r="Q16">
-        <v>281.37883124</v>
+        <v>280.2166049</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08219351161229956</v>
+        <v>0.08258432607896309</v>
       </c>
       <c r="T16">
-        <v>0.7294591721343968</v>
+        <v>0.737292524418384</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.328914213781404</v>
+        <v>6.840319932862644</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07752717716711863</v>
+        <v>0.07752613434765962</v>
       </c>
       <c r="C17">
-        <v>2028.118920890096</v>
+        <v>2004.366684299683</v>
       </c>
       <c r="D17">
-        <v>2340.848920890096</v>
+        <v>2340.878684299683</v>
       </c>
       <c r="E17">
-        <v>103.33</v>
+        <v>127.1120000000001</v>
       </c>
       <c r="F17">
-        <v>356.73</v>
+        <v>380.5120000000001</v>
       </c>
       <c r="G17">
         <v>44</v>
@@ -2687,28 +2687,28 @@
         <v>132.5</v>
       </c>
       <c r="M17">
-        <v>19.370439</v>
+        <v>20.6618016</v>
       </c>
       <c r="N17">
-        <v>113.129561</v>
+        <v>111.8381984</v>
       </c>
       <c r="O17">
-        <v>11.3129561</v>
+        <v>11.18381984</v>
       </c>
       <c r="P17">
-        <v>101.8166049</v>
+        <v>100.65437856</v>
       </c>
       <c r="Q17">
-        <v>280.2166049</v>
+        <v>279.05437856</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08258432607896309</v>
+        <v>0.08298444565197574</v>
       </c>
       <c r="T17">
-        <v>0.737292524418384</v>
+        <v>0.745312385090085</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.840319932862645</v>
+        <v>6.412799937058729</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07752613434765962</v>
+        <v>0.0776780915282006</v>
       </c>
       <c r="C18">
-        <v>2004.366684299683</v>
+        <v>1976.255596438219</v>
       </c>
       <c r="D18">
-        <v>2340.878684299683</v>
+        <v>2336.549596438219</v>
       </c>
       <c r="E18">
-        <v>127.1120000000001</v>
+        <v>150.8940000000001</v>
       </c>
       <c r="F18">
-        <v>380.5120000000001</v>
+        <v>404.2940000000001</v>
       </c>
       <c r="G18">
         <v>44</v>
@@ -2769,45 +2769,45 @@
         <v>132.5</v>
       </c>
       <c r="M18">
-        <v>20.6618016</v>
+        <v>22.35745820000001</v>
       </c>
       <c r="N18">
-        <v>111.8381984</v>
+        <v>110.1425418</v>
       </c>
       <c r="O18">
-        <v>11.18381984</v>
+        <v>11.01425418</v>
       </c>
       <c r="P18">
-        <v>100.65437856</v>
+        <v>99.12828761999997</v>
       </c>
       <c r="Q18">
-        <v>279.05437856</v>
+        <v>277.52828762</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08298444565197574</v>
+        <v>0.08339420666048267</v>
       </c>
       <c r="T18">
-        <v>0.745312385090085</v>
+        <v>0.7535254954165259</v>
       </c>
       <c r="U18">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V18">
         <v>0.1</v>
       </c>
       <c r="W18">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>6.412799937058729</v>
+        <v>5.926433980764411</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0776780915282006</v>
+        <v>0.0776860487087416</v>
       </c>
       <c r="C19">
-        <v>1976.255596438219</v>
+        <v>1952.247346522049</v>
       </c>
       <c r="D19">
-        <v>2336.549596438219</v>
+        <v>2336.323346522049</v>
       </c>
       <c r="E19">
-        <v>150.8940000000001</v>
+        <v>174.6760000000001</v>
       </c>
       <c r="F19">
-        <v>404.2940000000001</v>
+        <v>428.0760000000001</v>
       </c>
       <c r="G19">
         <v>44</v>
@@ -2851,28 +2851,28 @@
         <v>132.5</v>
       </c>
       <c r="M19">
-        <v>22.35745820000001</v>
+        <v>23.6726028</v>
       </c>
       <c r="N19">
-        <v>110.1425418</v>
+        <v>108.8273972</v>
       </c>
       <c r="O19">
-        <v>11.01425418</v>
+        <v>10.88273972</v>
       </c>
       <c r="P19">
-        <v>99.12828761999997</v>
+        <v>97.94465747999996</v>
       </c>
       <c r="Q19">
-        <v>277.52828762</v>
+        <v>276.34465748</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08339420666048267</v>
+        <v>0.08381396183992879</v>
       </c>
       <c r="T19">
-        <v>0.7535254954165259</v>
+        <v>0.7619389255070262</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.926433980764411</v>
+        <v>5.597187648499722</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0776860487087416</v>
+        <v>0.0776940058892826</v>
       </c>
       <c r="C20">
-        <v>1952.247346522049</v>
+        <v>1928.239140417548</v>
       </c>
       <c r="D20">
-        <v>2336.323346522049</v>
+        <v>2336.097140417548</v>
       </c>
       <c r="E20">
-        <v>174.676</v>
+        <v>198.4580000000001</v>
       </c>
       <c r="F20">
-        <v>428.076</v>
+        <v>451.8580000000001</v>
       </c>
       <c r="G20">
         <v>44</v>
@@ -2933,28 +2933,28 @@
         <v>132.5</v>
       </c>
       <c r="M20">
-        <v>23.6726028</v>
+        <v>24.9877474</v>
       </c>
       <c r="N20">
-        <v>108.8273972</v>
+        <v>107.5122526</v>
       </c>
       <c r="O20">
-        <v>10.88273972</v>
+        <v>10.75122526</v>
       </c>
       <c r="P20">
-        <v>97.94465747999996</v>
+        <v>96.76102733999997</v>
       </c>
       <c r="Q20">
-        <v>276.34465748</v>
+        <v>275.16102734</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08381396183992879</v>
+        <v>0.08424408134479333</v>
       </c>
       <c r="T20">
-        <v>0.7619389255070262</v>
+        <v>0.7705600946121068</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.597187648499722</v>
+        <v>5.302598824894474</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0776940058892826</v>
+        <v>0.0777019630698236</v>
       </c>
       <c r="C21">
-        <v>1928.239140417548</v>
+        <v>1904.23097811199</v>
       </c>
       <c r="D21">
-        <v>2336.097140417548</v>
+        <v>2335.870978111991</v>
       </c>
       <c r="E21">
-        <v>198.4580000000001</v>
+        <v>222.2400000000001</v>
       </c>
       <c r="F21">
-        <v>451.8580000000001</v>
+        <v>475.6400000000001</v>
       </c>
       <c r="G21">
         <v>44</v>
@@ -3015,28 +3015,28 @@
         <v>132.5</v>
       </c>
       <c r="M21">
-        <v>24.9877474</v>
+        <v>26.30289200000001</v>
       </c>
       <c r="N21">
-        <v>107.5122526</v>
+        <v>106.197108</v>
       </c>
       <c r="O21">
-        <v>10.75122526</v>
+        <v>10.6197108</v>
       </c>
       <c r="P21">
-        <v>96.76102733999997</v>
+        <v>95.57739719999996</v>
       </c>
       <c r="Q21">
-        <v>275.16102734</v>
+        <v>273.9773972</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08424408134479333</v>
+        <v>0.0846849538372795</v>
       </c>
       <c r="T21">
-        <v>0.7705600946121068</v>
+        <v>0.7793967929448146</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.302598824894474</v>
+        <v>5.037468883649749</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0777019630698236</v>
+        <v>0.07770992025036458</v>
       </c>
       <c r="C22">
-        <v>1904.23097811199</v>
+        <v>1880.222859592659</v>
       </c>
       <c r="D22">
-        <v>2335.870978111991</v>
+        <v>2335.644859592659</v>
       </c>
       <c r="E22">
-        <v>222.2400000000001</v>
+        <v>246.0220000000001</v>
       </c>
       <c r="F22">
-        <v>475.6400000000001</v>
+        <v>499.4220000000001</v>
       </c>
       <c r="G22">
         <v>44</v>
@@ -3097,28 +3097,28 @@
         <v>132.5</v>
       </c>
       <c r="M22">
-        <v>26.30289200000001</v>
+        <v>27.61803660000001</v>
       </c>
       <c r="N22">
-        <v>106.197108</v>
+        <v>104.8819634</v>
       </c>
       <c r="O22">
-        <v>10.6197108</v>
+        <v>10.48819634</v>
       </c>
       <c r="P22">
-        <v>95.57739719999996</v>
+        <v>94.39376705999996</v>
       </c>
       <c r="Q22">
-        <v>273.9773972</v>
+        <v>272.7937670599999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0846849538372795</v>
+        <v>0.08513698765868935</v>
       </c>
       <c r="T22">
-        <v>0.7793967929448146</v>
+        <v>0.7884572051593628</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.037468883649749</v>
+        <v>4.797589412999762</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07770992025036458</v>
+        <v>0.07771787743090559</v>
       </c>
       <c r="C23">
-        <v>1880.222859592659</v>
+        <v>1856.214784846835</v>
       </c>
       <c r="D23">
-        <v>2335.644859592659</v>
+        <v>2335.418784846835</v>
       </c>
       <c r="E23">
-        <v>246.022</v>
+        <v>269.8040000000001</v>
       </c>
       <c r="F23">
-        <v>499.422</v>
+        <v>523.2040000000001</v>
       </c>
       <c r="G23">
         <v>44</v>
@@ -3179,28 +3179,28 @@
         <v>132.5</v>
       </c>
       <c r="M23">
-        <v>27.6180366</v>
+        <v>28.9331812</v>
       </c>
       <c r="N23">
-        <v>104.8819634</v>
+        <v>103.5668188</v>
       </c>
       <c r="O23">
-        <v>10.48819634</v>
+        <v>10.35668188</v>
       </c>
       <c r="P23">
-        <v>94.39376705999996</v>
+        <v>93.21013691999997</v>
       </c>
       <c r="Q23">
-        <v>272.7937670599999</v>
+        <v>271.6101369199999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08513698765868935</v>
+        <v>0.08560061209090461</v>
       </c>
       <c r="T23">
-        <v>0.7884572051593628</v>
+        <v>0.7977499356358227</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.797589412999763</v>
+        <v>4.579517166954318</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07771787743090559</v>
+        <v>0.0782433346114466</v>
       </c>
       <c r="C24">
-        <v>1856.214784846835</v>
+        <v>1817.600056566437</v>
       </c>
       <c r="D24">
-        <v>2335.418784846835</v>
+        <v>2320.586056566437</v>
       </c>
       <c r="E24">
-        <v>269.8040000000001</v>
+        <v>293.5860000000001</v>
       </c>
       <c r="F24">
-        <v>523.2040000000001</v>
+        <v>546.9860000000001</v>
       </c>
       <c r="G24">
         <v>44</v>
@@ -3261,45 +3261,45 @@
         <v>132.5</v>
       </c>
       <c r="M24">
-        <v>28.9331812</v>
+        <v>31.61579080000001</v>
       </c>
       <c r="N24">
-        <v>103.5668188</v>
+        <v>100.8842092</v>
       </c>
       <c r="O24">
-        <v>10.35668188</v>
+        <v>10.08842092</v>
       </c>
       <c r="P24">
-        <v>93.21013691999997</v>
+        <v>90.79578827999995</v>
       </c>
       <c r="Q24">
-        <v>271.6101369199999</v>
+        <v>269.19578828</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08560061209090461</v>
+        <v>0.08607627871616441</v>
       </c>
       <c r="T24">
-        <v>0.7977499356358227</v>
+        <v>0.8072840357350478</v>
       </c>
       <c r="U24">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V24">
         <v>0.1</v>
       </c>
       <c r="W24">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.579517166954318</v>
+        <v>4.190943722970229</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0782433346114466</v>
+        <v>0.0782737917919876</v>
       </c>
       <c r="C25">
-        <v>1817.600056566437</v>
+        <v>1792.964078991133</v>
       </c>
       <c r="D25">
-        <v>2320.586056566437</v>
+        <v>2319.732078991133</v>
       </c>
       <c r="E25">
-        <v>293.5860000000001</v>
+        <v>317.3680000000002</v>
       </c>
       <c r="F25">
-        <v>546.9860000000001</v>
+        <v>570.7680000000001</v>
       </c>
       <c r="G25">
         <v>44</v>
@@ -3343,28 +3343,28 @@
         <v>132.5</v>
       </c>
       <c r="M25">
-        <v>31.61579080000001</v>
+        <v>32.99039040000001</v>
       </c>
       <c r="N25">
-        <v>100.8842092</v>
+        <v>99.50960959999996</v>
       </c>
       <c r="O25">
-        <v>10.08842092</v>
+        <v>9.950960959999996</v>
       </c>
       <c r="P25">
-        <v>90.79578827999995</v>
+        <v>89.55864863999997</v>
       </c>
       <c r="Q25">
-        <v>269.19578828</v>
+        <v>267.95864864</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08607627871616441</v>
+        <v>0.0865644628841942</v>
       </c>
       <c r="T25">
-        <v>0.8072840357350478</v>
+        <v>0.817069033205305</v>
       </c>
       <c r="U25">
         <v>0.0578</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.190943722970229</v>
+        <v>4.016321067846469</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0782737917919876</v>
+        <v>0.07909174897252859</v>
       </c>
       <c r="C26">
-        <v>1792.964078991133</v>
+        <v>1746.480481555111</v>
       </c>
       <c r="D26">
-        <v>2319.732078991133</v>
+        <v>2297.030481555111</v>
       </c>
       <c r="E26">
-        <v>317.3680000000001</v>
+        <v>341.1500000000001</v>
       </c>
       <c r="F26">
-        <v>570.768</v>
+        <v>594.5500000000001</v>
       </c>
       <c r="G26">
         <v>44</v>
@@ -3425,45 +3425,45 @@
         <v>132.5</v>
       </c>
       <c r="M26">
-        <v>32.9903904</v>
+        <v>36.44591500000001</v>
       </c>
       <c r="N26">
-        <v>99.50960959999998</v>
+        <v>96.05408499999996</v>
       </c>
       <c r="O26">
-        <v>9.950960959999998</v>
+        <v>9.605408499999996</v>
       </c>
       <c r="P26">
-        <v>89.55864863999997</v>
+        <v>86.44867649999996</v>
       </c>
       <c r="Q26">
-        <v>267.95864864</v>
+        <v>264.8486765</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.0865644628841942</v>
+        <v>0.08706566529670479</v>
       </c>
       <c r="T26">
-        <v>0.817069033205305</v>
+        <v>0.8271149639414359</v>
       </c>
       <c r="U26">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V26">
         <v>0.1</v>
       </c>
       <c r="W26">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.016321067846471</v>
+        <v>3.635524036095676</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07909174897252859</v>
+        <v>0.07980890615306957</v>
       </c>
       <c r="C27">
-        <v>1746.480481555111</v>
+        <v>1703.156947680851</v>
       </c>
       <c r="D27">
-        <v>2297.030481555111</v>
+        <v>2277.488947680851</v>
       </c>
       <c r="E27">
-        <v>341.1500000000001</v>
+        <v>364.9320000000001</v>
       </c>
       <c r="F27">
-        <v>594.5500000000001</v>
+        <v>618.3320000000001</v>
       </c>
       <c r="G27">
         <v>44</v>
@@ -3507,45 +3507,45 @@
         <v>132.5</v>
       </c>
       <c r="M27">
-        <v>36.44591500000001</v>
+        <v>39.63508120000001</v>
       </c>
       <c r="N27">
-        <v>96.05408499999996</v>
+        <v>92.86491879999997</v>
       </c>
       <c r="O27">
-        <v>9.605408499999996</v>
+        <v>9.286491879999998</v>
       </c>
       <c r="P27">
-        <v>86.44867649999996</v>
+        <v>83.57842691999997</v>
       </c>
       <c r="Q27">
-        <v>264.8486765</v>
+        <v>261.9784269199999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08706566529670479</v>
+        <v>0.08758041372036429</v>
       </c>
       <c r="T27">
-        <v>0.8271149639414359</v>
+        <v>0.8374324063190838</v>
       </c>
       <c r="U27">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V27">
         <v>0.1</v>
       </c>
       <c r="W27">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>3.635524036095676</v>
+        <v>3.342998071112819</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07980890615306957</v>
+        <v>0.07989606333361059</v>
       </c>
       <c r="C28">
-        <v>1703.156947680851</v>
+        <v>1677.022672080102</v>
       </c>
       <c r="D28">
-        <v>2277.488947680851</v>
+        <v>2275.136672080102</v>
       </c>
       <c r="E28">
-        <v>364.9320000000001</v>
+        <v>388.7140000000002</v>
       </c>
       <c r="F28">
-        <v>618.3320000000001</v>
+        <v>642.1140000000001</v>
       </c>
       <c r="G28">
         <v>44</v>
@@ -3589,28 +3589,28 @@
         <v>132.5</v>
       </c>
       <c r="M28">
-        <v>39.63508120000001</v>
+        <v>41.15950740000001</v>
       </c>
       <c r="N28">
-        <v>92.86491879999997</v>
+        <v>91.34049259999996</v>
       </c>
       <c r="O28">
-        <v>9.286491879999998</v>
+        <v>9.134049259999996</v>
       </c>
       <c r="P28">
-        <v>83.57842691999997</v>
+        <v>82.20644333999996</v>
       </c>
       <c r="Q28">
-        <v>261.9784269199999</v>
+        <v>260.6064433399999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08758041372036429</v>
+        <v>0.08810926484056245</v>
       </c>
       <c r="T28">
-        <v>0.8374324063190838</v>
+        <v>0.8480325183509138</v>
       </c>
       <c r="U28">
         <v>0.0641</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.342998071112819</v>
+        <v>3.21918332773827</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07989606333361059</v>
+        <v>0.07998322051415158</v>
       </c>
       <c r="C29">
-        <v>1677.022672080102</v>
+        <v>1650.893250502033</v>
       </c>
       <c r="D29">
-        <v>2275.136672080102</v>
+        <v>2272.789250502034</v>
       </c>
       <c r="E29">
-        <v>388.7140000000002</v>
+        <v>412.4960000000002</v>
       </c>
       <c r="F29">
-        <v>642.1140000000001</v>
+        <v>665.8960000000002</v>
       </c>
       <c r="G29">
         <v>44</v>
@@ -3671,28 +3671,28 @@
         <v>132.5</v>
       </c>
       <c r="M29">
-        <v>41.15950740000001</v>
+        <v>42.68393360000002</v>
       </c>
       <c r="N29">
-        <v>91.34049259999996</v>
+        <v>89.81606639999995</v>
       </c>
       <c r="O29">
-        <v>9.134049259999996</v>
+        <v>8.981606639999995</v>
       </c>
       <c r="P29">
-        <v>82.20644333999996</v>
+        <v>80.83445975999996</v>
       </c>
       <c r="Q29">
-        <v>260.6064433399999</v>
+        <v>259.2344597599999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08810926484056245</v>
+        <v>0.08865280626965497</v>
       </c>
       <c r="T29">
-        <v>0.8480325183509138</v>
+        <v>0.8589270779391834</v>
       </c>
       <c r="U29">
         <v>0.0641</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.21918332773827</v>
+        <v>3.10421249460476</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07998322051415158</v>
+        <v>0.08210617769469258</v>
       </c>
       <c r="C30">
-        <v>1650.893250502033</v>
+        <v>1571.39252526157</v>
       </c>
       <c r="D30">
-        <v>2272.789250502034</v>
+        <v>2217.07052526157</v>
       </c>
       <c r="E30">
-        <v>412.4960000000002</v>
+        <v>436.2780000000001</v>
       </c>
       <c r="F30">
-        <v>665.8960000000002</v>
+        <v>689.6780000000001</v>
       </c>
       <c r="G30">
         <v>44</v>
@@ -3753,45 +3753,45 @@
         <v>132.5</v>
       </c>
       <c r="M30">
-        <v>42.68393360000002</v>
+        <v>49.58784820000001</v>
       </c>
       <c r="N30">
-        <v>89.81606639999995</v>
+        <v>82.91215179999996</v>
       </c>
       <c r="O30">
-        <v>8.981606639999995</v>
+        <v>8.291215179999996</v>
       </c>
       <c r="P30">
-        <v>80.83445975999996</v>
+        <v>74.62093661999997</v>
       </c>
       <c r="Q30">
-        <v>259.2344597599999</v>
+        <v>253.02093662</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08865280626965497</v>
+        <v>0.08921165872491912</v>
       </c>
       <c r="T30">
-        <v>0.8589270779391834</v>
+        <v>0.8701285265299397</v>
       </c>
       <c r="U30">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V30">
         <v>0.1</v>
       </c>
       <c r="W30">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.10421249460476</v>
+        <v>2.672025603240431</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08210617769469257</v>
+        <v>0.08226353487523355</v>
       </c>
       <c r="C31">
-        <v>1571.39252526157</v>
+        <v>1543.589114937814</v>
       </c>
       <c r="D31">
-        <v>2217.07052526157</v>
+        <v>2213.049114937814</v>
       </c>
       <c r="E31">
-        <v>436.278</v>
+        <v>460.0600000000001</v>
       </c>
       <c r="F31">
-        <v>689.678</v>
+        <v>713.46</v>
       </c>
       <c r="G31">
         <v>44</v>
@@ -3835,28 +3835,28 @@
         <v>132.5</v>
       </c>
       <c r="M31">
-        <v>49.5878482</v>
+        <v>51.297774</v>
       </c>
       <c r="N31">
-        <v>82.91215179999998</v>
+        <v>81.20222599999997</v>
       </c>
       <c r="O31">
-        <v>8.291215179999998</v>
+        <v>8.120222599999996</v>
       </c>
       <c r="P31">
-        <v>74.62093661999998</v>
+        <v>73.08200339999998</v>
       </c>
       <c r="Q31">
-        <v>253.02093662</v>
+        <v>251.4820034</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08921165872491911</v>
+        <v>0.0897864783931908</v>
       </c>
       <c r="T31">
-        <v>0.8701285265299395</v>
+        <v>0.881650016509003</v>
       </c>
       <c r="U31">
         <v>0.07190000000000001</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.672025603240432</v>
+        <v>2.582958083132417</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08226353487523355</v>
+        <v>0.08350899205577456</v>
       </c>
       <c r="C32">
-        <v>1543.589114937814</v>
+        <v>1488.485679505865</v>
       </c>
       <c r="D32">
-        <v>2213.049114937814</v>
+        <v>2181.727679505866</v>
       </c>
       <c r="E32">
-        <v>460.0600000000001</v>
+        <v>483.8420000000001</v>
       </c>
       <c r="F32">
-        <v>713.46</v>
+        <v>737.2420000000001</v>
       </c>
       <c r="G32">
         <v>44</v>
@@ -3917,45 +3917,45 @@
         <v>132.5</v>
       </c>
       <c r="M32">
-        <v>51.297774</v>
+        <v>55.88294360000001</v>
       </c>
       <c r="N32">
-        <v>81.20222599999997</v>
+        <v>76.61705639999997</v>
       </c>
       <c r="O32">
-        <v>8.120222599999996</v>
+        <v>7.661705639999997</v>
       </c>
       <c r="P32">
-        <v>73.08200339999998</v>
+        <v>68.95535075999997</v>
       </c>
       <c r="Q32">
-        <v>251.4820034</v>
+        <v>247.35535076</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.0897864783931908</v>
+        <v>0.09037795950112255</v>
       </c>
       <c r="T32">
-        <v>0.881650016509003</v>
+        <v>0.8935054627193438</v>
       </c>
       <c r="U32">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V32">
         <v>0.1</v>
       </c>
       <c r="W32">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.582958083132417</v>
+        <v>2.371027570566271</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08350899205577456</v>
+        <v>0.08370144923631556</v>
       </c>
       <c r="C33">
-        <v>1488.485679505865</v>
+        <v>1459.94257533205</v>
       </c>
       <c r="D33">
-        <v>2181.727679505866</v>
+        <v>2176.966575332051</v>
       </c>
       <c r="E33">
-        <v>483.8420000000001</v>
+        <v>507.6240000000001</v>
       </c>
       <c r="F33">
-        <v>737.2420000000001</v>
+        <v>761.0240000000001</v>
       </c>
       <c r="G33">
         <v>44</v>
@@ -3999,28 +3999,28 @@
         <v>132.5</v>
       </c>
       <c r="M33">
-        <v>55.88294360000001</v>
+        <v>57.68561920000001</v>
       </c>
       <c r="N33">
-        <v>76.61705639999997</v>
+        <v>74.81438079999995</v>
       </c>
       <c r="O33">
-        <v>7.661705639999997</v>
+        <v>7.481438079999996</v>
       </c>
       <c r="P33">
-        <v>68.95535075999997</v>
+        <v>67.33294271999996</v>
       </c>
       <c r="Q33">
-        <v>247.35535076</v>
+        <v>245.73294272</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09037795950112255</v>
+        <v>0.09098683711222877</v>
       </c>
       <c r="T33">
-        <v>0.8935054627193438</v>
+        <v>0.9057095985241063</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.371027570566271</v>
+        <v>2.296932958986075</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08370144923631556</v>
+        <v>0.08389390641685654</v>
       </c>
       <c r="C34">
-        <v>1459.94257533205</v>
+        <v>1431.420205875124</v>
       </c>
       <c r="D34">
-        <v>2176.966575332051</v>
+        <v>2172.226205875124</v>
       </c>
       <c r="E34">
-        <v>507.6240000000001</v>
+        <v>531.4060000000002</v>
       </c>
       <c r="F34">
-        <v>761.0240000000001</v>
+        <v>784.8060000000002</v>
       </c>
       <c r="G34">
         <v>44</v>
@@ -4081,28 +4081,28 @@
         <v>132.5</v>
       </c>
       <c r="M34">
-        <v>57.68561920000001</v>
+        <v>59.48829480000002</v>
       </c>
       <c r="N34">
-        <v>74.81438079999995</v>
+        <v>73.01170519999995</v>
       </c>
       <c r="O34">
-        <v>7.481438079999996</v>
+        <v>7.301170519999996</v>
       </c>
       <c r="P34">
-        <v>67.33294271999996</v>
+        <v>65.71053467999995</v>
       </c>
       <c r="Q34">
-        <v>245.73294272</v>
+        <v>244.1105346799999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09098683711222877</v>
+        <v>0.09161389017441277</v>
       </c>
       <c r="T34">
-        <v>0.9057095985241063</v>
+        <v>0.9182780368902048</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.296932958986075</v>
+        <v>2.227328929925891</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08389390641685654</v>
+        <v>0.08408636359739755</v>
       </c>
       <c r="C35">
-        <v>1431.420205875124</v>
+        <v>1402.918435979143</v>
       </c>
       <c r="D35">
-        <v>2172.226205875124</v>
+        <v>2167.506435979144</v>
       </c>
       <c r="E35">
-        <v>531.4060000000002</v>
+        <v>555.1880000000002</v>
       </c>
       <c r="F35">
-        <v>784.8060000000002</v>
+        <v>808.5880000000002</v>
       </c>
       <c r="G35">
         <v>44</v>
@@ -4163,28 +4163,28 @@
         <v>132.5</v>
       </c>
       <c r="M35">
-        <v>59.48829480000002</v>
+        <v>61.29097040000002</v>
       </c>
       <c r="N35">
-        <v>73.01170519999995</v>
+        <v>71.20902959999995</v>
       </c>
       <c r="O35">
-        <v>7.301170519999996</v>
+        <v>7.120902959999995</v>
       </c>
       <c r="P35">
-        <v>65.71053467999995</v>
+        <v>64.08812663999996</v>
       </c>
       <c r="Q35">
-        <v>244.1105346799999</v>
+        <v>242.48812664</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09161389017441277</v>
+        <v>0.09225994484454175</v>
       </c>
       <c r="T35">
-        <v>0.9182780368902048</v>
+        <v>0.9312273370249733</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.227328929925891</v>
+        <v>2.161819255516305</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08408636359739755</v>
+        <v>0.08427882077793855</v>
       </c>
       <c r="C36">
-        <v>1402.918435979143</v>
+        <v>1374.437131660278</v>
       </c>
       <c r="D36">
-        <v>2167.506435979144</v>
+        <v>2162.807131660278</v>
       </c>
       <c r="E36">
-        <v>555.1880000000002</v>
+        <v>578.9700000000001</v>
       </c>
       <c r="F36">
-        <v>808.5880000000002</v>
+        <v>832.3700000000001</v>
       </c>
       <c r="G36">
         <v>44</v>
@@ -4245,28 +4245,28 @@
         <v>132.5</v>
       </c>
       <c r="M36">
-        <v>61.29097040000002</v>
+        <v>63.09364600000001</v>
       </c>
       <c r="N36">
-        <v>71.20902959999995</v>
+        <v>69.40635399999996</v>
       </c>
       <c r="O36">
-        <v>7.120902959999995</v>
+        <v>6.940635399999997</v>
       </c>
       <c r="P36">
-        <v>64.08812663999996</v>
+        <v>62.46571859999997</v>
       </c>
       <c r="Q36">
-        <v>242.48812664</v>
+        <v>240.8657186</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09225994484454175</v>
+        <v>0.09292587811990546</v>
       </c>
       <c r="T36">
-        <v>0.9312273370249733</v>
+        <v>0.9445750771638883</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.161819255516305</v>
+        <v>2.100052991072983</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08427882077793855</v>
+        <v>0.08447127795847953</v>
       </c>
       <c r="C37">
-        <v>1374.437131660278</v>
+        <v>1345.976160094127</v>
       </c>
       <c r="D37">
-        <v>2162.807131660278</v>
+        <v>2158.128160094127</v>
       </c>
       <c r="E37">
-        <v>578.9700000000001</v>
+        <v>602.7520000000002</v>
       </c>
       <c r="F37">
-        <v>832.3700000000001</v>
+        <v>856.1520000000002</v>
       </c>
       <c r="G37">
         <v>44</v>
@@ -4327,28 +4327,28 @@
         <v>132.5</v>
       </c>
       <c r="M37">
-        <v>63.09364600000001</v>
+        <v>64.89632160000002</v>
       </c>
       <c r="N37">
-        <v>69.40635399999996</v>
+        <v>67.60367839999995</v>
       </c>
       <c r="O37">
-        <v>6.940635399999997</v>
+        <v>6.760367839999995</v>
       </c>
       <c r="P37">
-        <v>62.46571859999997</v>
+        <v>60.84331055999996</v>
       </c>
       <c r="Q37">
-        <v>240.8657186</v>
+        <v>239.24331056</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09292587811990546</v>
+        <v>0.09361262181012428</v>
       </c>
       <c r="T37">
-        <v>0.9445750771638883</v>
+        <v>0.9583399341821445</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.100052991072983</v>
+        <v>2.0417181857654</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08447127795847954</v>
+        <v>0.08939233513902053</v>
       </c>
       <c r="C38">
-        <v>1345.976160094126</v>
+        <v>1209.07106150418</v>
       </c>
       <c r="D38">
-        <v>2158.128160094127</v>
+        <v>2045.005061504181</v>
       </c>
       <c r="E38">
-        <v>602.7520000000001</v>
+        <v>626.5340000000001</v>
       </c>
       <c r="F38">
-        <v>856.152</v>
+        <v>879.9340000000001</v>
       </c>
       <c r="G38">
         <v>44</v>
@@ -4409,45 +4409,45 @@
         <v>132.5</v>
       </c>
       <c r="M38">
-        <v>64.89632160000001</v>
+        <v>79.19406000000001</v>
       </c>
       <c r="N38">
-        <v>67.60367839999996</v>
+        <v>53.30593999999996</v>
       </c>
       <c r="O38">
-        <v>6.760367839999997</v>
+        <v>5.330593999999997</v>
       </c>
       <c r="P38">
-        <v>60.84331055999996</v>
+        <v>47.97534599999997</v>
       </c>
       <c r="Q38">
-        <v>239.24331056</v>
+        <v>226.375346</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09361262181012428</v>
+        <v>0.09432116688733419</v>
       </c>
       <c r="T38">
-        <v>0.9583399341821445</v>
+        <v>0.9725417707882816</v>
       </c>
       <c r="U38">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V38">
         <v>0.1</v>
       </c>
       <c r="W38">
-        <v>0.06822</v>
+        <v>0.081</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.0417181857654</v>
+        <v>1.673105280875863</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08939233513902053</v>
+        <v>0.08971259231956154</v>
       </c>
       <c r="C39">
-        <v>1209.07106150418</v>
+        <v>1178.336738463947</v>
       </c>
       <c r="D39">
-        <v>2045.005061504181</v>
+        <v>2038.052738463947</v>
       </c>
       <c r="E39">
-        <v>626.5340000000001</v>
+        <v>650.3160000000001</v>
       </c>
       <c r="F39">
-        <v>879.9340000000001</v>
+        <v>903.7160000000001</v>
       </c>
       <c r="G39">
         <v>44</v>
@@ -4491,28 +4491,28 @@
         <v>132.5</v>
       </c>
       <c r="M39">
-        <v>79.19406000000001</v>
+        <v>81.33444000000001</v>
       </c>
       <c r="N39">
-        <v>53.30593999999996</v>
+        <v>51.16555999999996</v>
       </c>
       <c r="O39">
-        <v>5.330593999999997</v>
+        <v>5.116555999999996</v>
       </c>
       <c r="P39">
-        <v>47.97534599999997</v>
+        <v>46.04900399999996</v>
       </c>
       <c r="Q39">
-        <v>226.375346</v>
+        <v>224.449004</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09432116688733419</v>
+        <v>0.09505256825735732</v>
       </c>
       <c r="T39">
-        <v>0.9725417707882816</v>
+        <v>0.9872017311559074</v>
       </c>
       <c r="U39">
         <v>0.09</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.673105280875863</v>
+        <v>1.629076194537024</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08971259231956154</v>
+        <v>0.09003284950010254</v>
       </c>
       <c r="C40">
-        <v>1178.336738463947</v>
+        <v>1147.649526339388</v>
       </c>
       <c r="D40">
-        <v>2038.052738463947</v>
+        <v>2031.147526339388</v>
       </c>
       <c r="E40">
-        <v>650.3160000000001</v>
+        <v>674.0980000000002</v>
       </c>
       <c r="F40">
-        <v>903.7160000000001</v>
+        <v>927.4980000000002</v>
       </c>
       <c r="G40">
         <v>44</v>
@@ -4573,28 +4573,28 @@
         <v>132.5</v>
       </c>
       <c r="M40">
-        <v>81.33444000000001</v>
+        <v>83.47482000000001</v>
       </c>
       <c r="N40">
-        <v>51.16555999999996</v>
+        <v>49.02517999999996</v>
       </c>
       <c r="O40">
-        <v>5.116555999999996</v>
+        <v>4.902517999999997</v>
       </c>
       <c r="P40">
-        <v>46.04900399999996</v>
+        <v>44.12266199999996</v>
       </c>
       <c r="Q40">
-        <v>224.449004</v>
+        <v>222.522662</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09505256825735732</v>
+        <v>0.09580795000016809</v>
       </c>
       <c r="T40">
-        <v>0.9872017311559074</v>
+        <v>1.002342345961816</v>
       </c>
       <c r="U40">
         <v>0.09</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.629076194537024</v>
+        <v>1.587305010061716</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09003284950010254</v>
+        <v>0.09035310668064353</v>
       </c>
       <c r="C41">
-        <v>1147.649526339388</v>
+        <v>1117.008947892036</v>
       </c>
       <c r="D41">
-        <v>2031.147526339388</v>
+        <v>2024.288947892036</v>
       </c>
       <c r="E41">
-        <v>674.0980000000002</v>
+        <v>697.8800000000002</v>
       </c>
       <c r="F41">
-        <v>927.4980000000002</v>
+        <v>951.2800000000002</v>
       </c>
       <c r="G41">
         <v>44</v>
@@ -4655,28 +4655,28 @@
         <v>132.5</v>
       </c>
       <c r="M41">
-        <v>83.47482000000001</v>
+        <v>85.61520000000002</v>
       </c>
       <c r="N41">
-        <v>49.02517999999996</v>
+        <v>46.88479999999996</v>
       </c>
       <c r="O41">
-        <v>4.902517999999997</v>
+        <v>4.688479999999996</v>
       </c>
       <c r="P41">
-        <v>44.12266199999996</v>
+        <v>42.19631999999996</v>
       </c>
       <c r="Q41">
-        <v>222.522662</v>
+        <v>220.59632</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09580795000016809</v>
+        <v>0.09658851113440589</v>
       </c>
       <c r="T41">
-        <v>1.002342345961816</v>
+        <v>1.017987647927921</v>
       </c>
       <c r="U41">
         <v>0.09</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.587305010061716</v>
+        <v>1.547622384810173</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09035310668064353</v>
+        <v>0.09067336386118452</v>
       </c>
       <c r="C42">
-        <v>1117.008947892036</v>
+        <v>1086.414532307699</v>
       </c>
       <c r="D42">
-        <v>2024.288947892036</v>
+        <v>2017.476532307699</v>
       </c>
       <c r="E42">
-        <v>697.8800000000002</v>
+        <v>721.6620000000003</v>
       </c>
       <c r="F42">
-        <v>951.2800000000002</v>
+        <v>975.0620000000002</v>
       </c>
       <c r="G42">
         <v>44</v>
@@ -4737,28 +4737,28 @@
         <v>132.5</v>
       </c>
       <c r="M42">
-        <v>85.61520000000002</v>
+        <v>87.75558000000002</v>
       </c>
       <c r="N42">
-        <v>46.88479999999996</v>
+        <v>44.74441999999995</v>
       </c>
       <c r="O42">
-        <v>4.688479999999996</v>
+        <v>4.474441999999995</v>
       </c>
       <c r="P42">
-        <v>42.19631999999996</v>
+        <v>40.26997799999995</v>
       </c>
       <c r="Q42">
-        <v>220.59632</v>
+        <v>218.669978</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09658851113440589</v>
+        <v>0.09739553196810936</v>
       </c>
       <c r="T42">
-        <v>1.017987647927921</v>
+        <v>1.034163299113216</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.547622384810173</v>
+        <v>1.509875497375779</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09067336386118452</v>
+        <v>0.1131866565805926</v>
       </c>
       <c r="C43">
-        <v>1086.414532307699</v>
+        <v>676.6596294016871</v>
       </c>
       <c r="D43">
-        <v>2017.476532307699</v>
+        <v>1631.503629401687</v>
       </c>
       <c r="E43">
-        <v>721.6620000000003</v>
+        <v>745.4440000000002</v>
       </c>
       <c r="F43">
-        <v>975.0620000000002</v>
+        <v>998.8440000000002</v>
       </c>
       <c r="G43">
         <v>44</v>
@@ -4819,45 +4819,45 @@
         <v>132.5</v>
       </c>
       <c r="M43">
-        <v>87.75558000000002</v>
+        <v>146.6302992</v>
       </c>
       <c r="N43">
-        <v>44.74441999999995</v>
+        <v>-14.13029920000005</v>
       </c>
       <c r="O43">
-        <v>4.474441999999995</v>
+        <v>-1.413029920000005</v>
       </c>
       <c r="P43">
-        <v>40.26997799999995</v>
+        <v>-12.71726928000005</v>
       </c>
       <c r="Q43">
-        <v>218.669978</v>
+        <v>165.68273072</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09739553196810936</v>
+        <v>0.09845189166536067</v>
       </c>
       <c r="T43">
-        <v>1.034163299113216</v>
+        <v>1.055336613698574</v>
       </c>
       <c r="U43">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.1</v>
+        <v>0.09036331557863994</v>
       </c>
       <c r="W43">
-        <v>0.081</v>
+        <v>0.1335346652730557</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y43">
-        <v>1.509875497375779</v>
+        <v>0.9036331557863994</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1131866565805926</v>
+        <v>0.1141966565805926</v>
       </c>
       <c r="C44">
-        <v>676.6596294016872</v>
+        <v>638.9938676464361</v>
       </c>
       <c r="D44">
-        <v>1631.503629401687</v>
+        <v>1617.619867646436</v>
       </c>
       <c r="E44">
-        <v>745.4440000000001</v>
+        <v>769.2260000000001</v>
       </c>
       <c r="F44">
-        <v>998.8440000000001</v>
+        <v>1022.626</v>
       </c>
       <c r="G44">
         <v>44</v>
@@ -4901,37 +4901,37 @@
         <v>132.5</v>
       </c>
       <c r="M44">
-        <v>146.6302992</v>
+        <v>150.1214968</v>
       </c>
       <c r="N44">
-        <v>-14.13029920000005</v>
+        <v>-17.62149680000005</v>
       </c>
       <c r="O44">
-        <v>-1.413029920000005</v>
+        <v>-1.762149680000005</v>
       </c>
       <c r="P44">
-        <v>-12.71726928000005</v>
+        <v>-15.85934712000004</v>
       </c>
       <c r="Q44">
-        <v>165.68273072</v>
+        <v>162.54065288</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09845189166536067</v>
+        <v>0.09937560906299857</v>
       </c>
       <c r="T44">
-        <v>1.055336613698574</v>
+        <v>1.073851291131882</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.09036331557863994</v>
+        <v>0.08826184312332275</v>
       </c>
       <c r="W44">
-        <v>0.1335346652730557</v>
+        <v>0.1338431614294962</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.9036331557863994</v>
+        <v>0.8826184312332274</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1141966565805926</v>
+        <v>0.1152066565805926</v>
       </c>
       <c r="C45">
-        <v>638.9938676464361</v>
+        <v>601.5624079668096</v>
       </c>
       <c r="D45">
-        <v>1617.619867646436</v>
+        <v>1603.97040796681</v>
       </c>
       <c r="E45">
-        <v>769.2260000000001</v>
+        <v>793.0080000000002</v>
       </c>
       <c r="F45">
-        <v>1022.626</v>
+        <v>1046.408</v>
       </c>
       <c r="G45">
         <v>44</v>
@@ -4983,37 +4983,37 @@
         <v>132.5</v>
       </c>
       <c r="M45">
-        <v>150.1214968</v>
+        <v>153.6126944</v>
       </c>
       <c r="N45">
-        <v>-17.62149680000005</v>
+        <v>-21.11269440000007</v>
       </c>
       <c r="O45">
-        <v>-1.762149680000005</v>
+        <v>-2.111269440000007</v>
       </c>
       <c r="P45">
-        <v>-15.85934712000004</v>
+        <v>-19.00142496000006</v>
       </c>
       <c r="Q45">
-        <v>162.54065288</v>
+        <v>159.3985750399999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09937560906299857</v>
+        <v>0.100332316367695</v>
       </c>
       <c r="T45">
-        <v>1.073851291131882</v>
+        <v>1.093027207044951</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.08826184312332275</v>
+        <v>0.08625589214324721</v>
       </c>
       <c r="W45">
-        <v>0.1338431614294962</v>
+        <v>0.1341376350333713</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8826184312332274</v>
+        <v>0.862558921432472</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1152066565805926</v>
+        <v>0.1162166565805926</v>
       </c>
       <c r="C46">
-        <v>601.5624079668096</v>
+        <v>564.359368875279</v>
       </c>
       <c r="D46">
-        <v>1603.97040796681</v>
+        <v>1590.549368875279</v>
       </c>
       <c r="E46">
-        <v>793.0080000000002</v>
+        <v>816.7900000000001</v>
       </c>
       <c r="F46">
-        <v>1046.408</v>
+        <v>1070.19</v>
       </c>
       <c r="G46">
         <v>44</v>
@@ -5065,37 +5065,37 @@
         <v>132.5</v>
       </c>
       <c r="M46">
-        <v>153.6126944</v>
+        <v>157.103892</v>
       </c>
       <c r="N46">
-        <v>-21.11269440000007</v>
+        <v>-24.60389200000006</v>
       </c>
       <c r="O46">
-        <v>-2.111269440000007</v>
+        <v>-2.460389200000006</v>
       </c>
       <c r="P46">
-        <v>-19.00142496000006</v>
+        <v>-22.14350280000005</v>
       </c>
       <c r="Q46">
-        <v>159.3985750399999</v>
+        <v>156.2564972</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.100332316367695</v>
+        <v>0.1013238130289258</v>
       </c>
       <c r="T46">
-        <v>1.093027207044951</v>
+        <v>1.112900428991223</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.08625589214324721</v>
+        <v>0.08433909454006394</v>
       </c>
       <c r="W46">
-        <v>0.1341376350333713</v>
+        <v>0.1344190209215186</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.862558921432472</v>
+        <v>0.8433909454006394</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1162166565805926</v>
+        <v>0.1172266565805926</v>
       </c>
       <c r="C47">
-        <v>564.359368875279</v>
+        <v>527.3790641015587</v>
       </c>
       <c r="D47">
-        <v>1590.549368875279</v>
+        <v>1577.351064101559</v>
       </c>
       <c r="E47">
-        <v>816.7900000000001</v>
+        <v>840.5720000000002</v>
       </c>
       <c r="F47">
-        <v>1070.19</v>
+        <v>1093.972</v>
       </c>
       <c r="G47">
         <v>44</v>
@@ -5147,37 +5147,37 @@
         <v>132.5</v>
       </c>
       <c r="M47">
-        <v>157.103892</v>
+        <v>160.5950896000001</v>
       </c>
       <c r="N47">
-        <v>-24.60389200000006</v>
+        <v>-28.09508960000008</v>
       </c>
       <c r="O47">
-        <v>-2.460389200000006</v>
+        <v>-2.809508960000008</v>
       </c>
       <c r="P47">
-        <v>-22.14350280000005</v>
+        <v>-25.28558064000007</v>
       </c>
       <c r="Q47">
-        <v>156.2564972</v>
+        <v>153.1144193599999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1013238130289258</v>
+        <v>0.1023520317887207</v>
       </c>
       <c r="T47">
-        <v>1.112900428991223</v>
+        <v>1.133509696194764</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.08433909454006394</v>
+        <v>0.08250563596310602</v>
       </c>
       <c r="W47">
-        <v>0.1344190209215186</v>
+        <v>0.1346881726406161</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8433909454006394</v>
+        <v>0.8250563596310602</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1172266565805926</v>
+        <v>0.1182366565805926</v>
       </c>
       <c r="C48">
-        <v>527.3790641015587</v>
+        <v>490.6159945597421</v>
       </c>
       <c r="D48">
-        <v>1577.351064101559</v>
+        <v>1564.369994559742</v>
       </c>
       <c r="E48">
-        <v>840.5720000000002</v>
+        <v>864.3540000000002</v>
       </c>
       <c r="F48">
-        <v>1093.972</v>
+        <v>1117.754</v>
       </c>
       <c r="G48">
         <v>44</v>
@@ -5229,37 +5229,37 @@
         <v>132.5</v>
       </c>
       <c r="M48">
-        <v>160.5950896000001</v>
+        <v>164.0862872</v>
       </c>
       <c r="N48">
-        <v>-28.09508960000008</v>
+        <v>-31.58628720000007</v>
       </c>
       <c r="O48">
-        <v>-2.809508960000008</v>
+        <v>-3.158628720000007</v>
       </c>
       <c r="P48">
-        <v>-25.28558064000007</v>
+        <v>-28.42765848000007</v>
       </c>
       <c r="Q48">
-        <v>153.1144193599999</v>
+        <v>149.9723415199999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1023520317887207</v>
+        <v>0.1034190512564324</v>
       </c>
       <c r="T48">
-        <v>1.133509696194764</v>
+        <v>1.154896671594666</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.08250563596310602</v>
+        <v>0.08075019690006122</v>
       </c>
       <c r="W48">
-        <v>0.1346881726406161</v>
+        <v>0.134945871095071</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8250563596310602</v>
+        <v>0.8075019690006121</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1182366565805926</v>
+        <v>0.1454906356833172</v>
       </c>
       <c r="C49">
-        <v>490.6159945597421</v>
+        <v>182.5621068183175</v>
       </c>
       <c r="D49">
-        <v>1564.369994559742</v>
+        <v>1280.098106818318</v>
       </c>
       <c r="E49">
-        <v>864.3540000000002</v>
+        <v>888.1360000000003</v>
       </c>
       <c r="F49">
-        <v>1117.754</v>
+        <v>1141.536</v>
       </c>
       <c r="G49">
         <v>44</v>
@@ -5311,45 +5311,45 @@
         <v>132.5</v>
       </c>
       <c r="M49">
-        <v>164.0862872</v>
+        <v>229.2204288000001</v>
       </c>
       <c r="N49">
-        <v>-31.58628720000007</v>
+        <v>-96.72042880000009</v>
       </c>
       <c r="O49">
-        <v>-3.158628720000007</v>
+        <v>-9.67204288000001</v>
       </c>
       <c r="P49">
-        <v>-28.42765848000007</v>
+        <v>-87.04838592000009</v>
       </c>
       <c r="Q49">
-        <v>149.9723415199999</v>
+        <v>91.35161407999992</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1034190512564324</v>
+        <v>0.1051501466704496</v>
       </c>
       <c r="T49">
-        <v>1.154896671594666</v>
+        <v>1.189594159461373</v>
       </c>
       <c r="U49">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.08075019690006122</v>
+        <v>0.05780462094659511</v>
       </c>
       <c r="W49">
-        <v>0.134945871095071</v>
+        <v>0.1891928321139237</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y49">
-        <v>0.8075019690006121</v>
+        <v>0.5780462094659511</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1454906356833172</v>
+        <v>0.1470406356833172</v>
       </c>
       <c r="C50">
-        <v>182.5621068183179</v>
+        <v>145.6860500675198</v>
       </c>
       <c r="D50">
-        <v>1280.098106818318</v>
+        <v>1267.00405006752</v>
       </c>
       <c r="E50">
-        <v>888.1360000000001</v>
+        <v>911.9180000000002</v>
       </c>
       <c r="F50">
-        <v>1141.536</v>
+        <v>1165.318</v>
       </c>
       <c r="G50">
         <v>44</v>
@@ -5393,37 +5393,37 @@
         <v>132.5</v>
       </c>
       <c r="M50">
-        <v>229.2204288</v>
+        <v>233.9958544</v>
       </c>
       <c r="N50">
-        <v>-96.72042880000004</v>
+        <v>-101.4958544000001</v>
       </c>
       <c r="O50">
-        <v>-9.672042880000005</v>
+        <v>-10.14958544000001</v>
       </c>
       <c r="P50">
-        <v>-87.04838592000003</v>
+        <v>-91.34626896000006</v>
       </c>
       <c r="Q50">
-        <v>91.35161407999998</v>
+        <v>87.05373103999995</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1051501466704496</v>
+        <v>0.1063138750365369</v>
       </c>
       <c r="T50">
-        <v>1.189594159461373</v>
+        <v>1.212919535137086</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.05780462094659514</v>
+        <v>0.05662493480482788</v>
       </c>
       <c r="W50">
-        <v>0.1891928321139237</v>
+        <v>0.1894297130911906</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5780462094659513</v>
+        <v>0.5662493480482786</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1470406356833172</v>
+        <v>0.1485906356833172</v>
       </c>
       <c r="C51">
-        <v>145.6860500675198</v>
+        <v>109.0751578097072</v>
       </c>
       <c r="D51">
-        <v>1267.00405006752</v>
+        <v>1254.175157809707</v>
       </c>
       <c r="E51">
-        <v>911.9180000000002</v>
+        <v>935.7000000000002</v>
       </c>
       <c r="F51">
-        <v>1165.318</v>
+        <v>1189.1</v>
       </c>
       <c r="G51">
         <v>44</v>
@@ -5475,37 +5475,37 @@
         <v>132.5</v>
       </c>
       <c r="M51">
-        <v>233.9958544</v>
+        <v>238.77128</v>
       </c>
       <c r="N51">
-        <v>-101.4958544000001</v>
+        <v>-106.2712800000001</v>
       </c>
       <c r="O51">
-        <v>-10.14958544000001</v>
+        <v>-10.62712800000001</v>
       </c>
       <c r="P51">
-        <v>-91.34626896000006</v>
+        <v>-95.64415200000006</v>
       </c>
       <c r="Q51">
-        <v>87.05373103999995</v>
+        <v>82.75584799999994</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1063138750365369</v>
+        <v>0.1075241525372676</v>
       </c>
       <c r="T51">
-        <v>1.212919535137086</v>
+        <v>1.237177925839828</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.05662493480482788</v>
+        <v>0.05549243610873131</v>
       </c>
       <c r="W51">
-        <v>0.1894297130911906</v>
+        <v>0.1896571188293668</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5662493480482786</v>
+        <v>0.5549243610873131</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1485906356833172</v>
+        <v>0.1501406356833172</v>
       </c>
       <c r="C52">
-        <v>109.0751578097072</v>
+        <v>72.72145611344376</v>
       </c>
       <c r="D52">
-        <v>1254.175157809707</v>
+        <v>1241.603456113444</v>
       </c>
       <c r="E52">
-        <v>935.7000000000002</v>
+        <v>959.4820000000001</v>
       </c>
       <c r="F52">
-        <v>1189.1</v>
+        <v>1212.882</v>
       </c>
       <c r="G52">
         <v>44</v>
@@ -5557,37 +5557,37 @@
         <v>132.5</v>
       </c>
       <c r="M52">
-        <v>238.77128</v>
+        <v>243.5467056</v>
       </c>
       <c r="N52">
-        <v>-106.2712800000001</v>
+        <v>-111.0467056000001</v>
       </c>
       <c r="O52">
-        <v>-10.62712800000001</v>
+        <v>-11.10467056000001</v>
       </c>
       <c r="P52">
-        <v>-95.64415200000006</v>
+        <v>-99.94203504000005</v>
       </c>
       <c r="Q52">
-        <v>82.75584799999994</v>
+        <v>78.45796495999996</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1075241525372676</v>
+        <v>0.1087838291196608</v>
       </c>
       <c r="T52">
-        <v>1.237177925839828</v>
+        <v>1.2624264549386</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.05549243610873131</v>
+        <v>0.05440434912620717</v>
       </c>
       <c r="W52">
-        <v>0.1896571188293668</v>
+        <v>0.1898756066954576</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5549243610873131</v>
+        <v>0.5440434912620717</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1501406356833172</v>
+        <v>0.1516906356833172</v>
       </c>
       <c r="C53">
-        <v>72.72145611344376</v>
+        <v>36.6172875932109</v>
       </c>
       <c r="D53">
-        <v>1241.603456113444</v>
+        <v>1229.281287593211</v>
       </c>
       <c r="E53">
-        <v>959.4820000000001</v>
+        <v>983.2640000000002</v>
       </c>
       <c r="F53">
-        <v>1212.882</v>
+        <v>1236.664</v>
       </c>
       <c r="G53">
         <v>44</v>
@@ -5639,37 +5639,37 @@
         <v>132.5</v>
       </c>
       <c r="M53">
-        <v>243.5467056</v>
+        <v>248.3221312000001</v>
       </c>
       <c r="N53">
-        <v>-111.0467056000001</v>
+        <v>-115.8221312000001</v>
       </c>
       <c r="O53">
-        <v>-11.10467056000001</v>
+        <v>-11.58221312000001</v>
       </c>
       <c r="P53">
-        <v>-99.94203504000005</v>
+        <v>-104.2399180800001</v>
       </c>
       <c r="Q53">
-        <v>78.45796495999996</v>
+        <v>74.16008191999993</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1087838291196608</v>
+        <v>0.1100959922263204</v>
       </c>
       <c r="T53">
-        <v>1.2624264549386</v>
+        <v>1.288727006083154</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.05440434912620717</v>
+        <v>0.05335811164301088</v>
       </c>
       <c r="W53">
-        <v>0.1898756066954576</v>
+        <v>0.1900856911820834</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5440434912620717</v>
+        <v>0.5335811164301087</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1516906356833172</v>
+        <v>0.1532406356833172</v>
       </c>
       <c r="C54">
-        <v>36.6172875932109</v>
+        <v>0.7552958561275318</v>
       </c>
       <c r="D54">
-        <v>1229.281287593211</v>
+        <v>1217.201295856128</v>
       </c>
       <c r="E54">
-        <v>983.2640000000002</v>
+        <v>1007.046</v>
       </c>
       <c r="F54">
-        <v>1236.664</v>
+        <v>1260.446</v>
       </c>
       <c r="G54">
         <v>44</v>
@@ -5721,37 +5721,37 @@
         <v>132.5</v>
       </c>
       <c r="M54">
-        <v>248.3221312000001</v>
+        <v>253.0975568</v>
       </c>
       <c r="N54">
-        <v>-115.8221312000001</v>
+        <v>-120.5975568000001</v>
       </c>
       <c r="O54">
-        <v>-11.58221312000001</v>
+        <v>-12.05975568000001</v>
       </c>
       <c r="P54">
-        <v>-104.2399180800001</v>
+        <v>-108.5378011200001</v>
       </c>
       <c r="Q54">
-        <v>74.16008191999993</v>
+        <v>69.86219887999995</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1100959922263204</v>
+        <v>0.111463992060923</v>
       </c>
       <c r="T54">
-        <v>1.288727006083154</v>
+        <v>1.316146729616838</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.05335811164301088</v>
+        <v>0.05235135481955785</v>
       </c>
       <c r="W54">
-        <v>0.1900856911820834</v>
+        <v>0.1902878479522328</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5335811164301087</v>
+        <v>0.5235135481955784</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1532406356833172</v>
+        <v>0.1547906356833172</v>
       </c>
       <c r="C55">
-        <v>0.7552958561275318</v>
+        <v>-34.87158914321958</v>
       </c>
       <c r="D55">
-        <v>1217.201295856128</v>
+        <v>1205.356410856781</v>
       </c>
       <c r="E55">
-        <v>1007.046</v>
+        <v>1030.828</v>
       </c>
       <c r="F55">
-        <v>1260.446</v>
+        <v>1284.228</v>
       </c>
       <c r="G55">
         <v>44</v>
@@ -5803,37 +5803,37 @@
         <v>132.5</v>
       </c>
       <c r="M55">
-        <v>253.0975568</v>
+        <v>257.8729824000001</v>
       </c>
       <c r="N55">
-        <v>-120.5975568000001</v>
+        <v>-125.3729824000001</v>
       </c>
       <c r="O55">
-        <v>-12.05975568000001</v>
+        <v>-12.53729824000001</v>
       </c>
       <c r="P55">
-        <v>-108.5378011200001</v>
+        <v>-112.8356841600001</v>
       </c>
       <c r="Q55">
-        <v>69.86219887999995</v>
+        <v>65.56431583999992</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.111463992060923</v>
+        <v>0.1128914701492039</v>
       </c>
       <c r="T55">
-        <v>1.316146729616838</v>
+        <v>1.344758615043291</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.05235135481955785</v>
+        <v>0.05138188528586233</v>
       </c>
       <c r="W55">
-        <v>0.1902878479522328</v>
+        <v>0.1904825174345988</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5235135481955784</v>
+        <v>0.5138188528586232</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1547906356833172</v>
+        <v>0.1563406356833172</v>
       </c>
       <c r="C56">
-        <v>-34.87158914321958</v>
+        <v>-70.27016490108599</v>
       </c>
       <c r="D56">
-        <v>1205.356410856781</v>
+        <v>1193.739835098914</v>
       </c>
       <c r="E56">
-        <v>1030.828</v>
+        <v>1054.61</v>
       </c>
       <c r="F56">
-        <v>1284.228</v>
+        <v>1308.01</v>
       </c>
       <c r="G56">
         <v>44</v>
@@ -5885,37 +5885,37 @@
         <v>132.5</v>
       </c>
       <c r="M56">
-        <v>257.8729824000001</v>
+        <v>262.6484080000001</v>
       </c>
       <c r="N56">
-        <v>-125.3729824000001</v>
+        <v>-130.1484080000001</v>
       </c>
       <c r="O56">
-        <v>-12.53729824000001</v>
+        <v>-13.01484080000001</v>
       </c>
       <c r="P56">
-        <v>-112.8356841600001</v>
+        <v>-117.1335672000001</v>
       </c>
       <c r="Q56">
-        <v>65.56431583999992</v>
+        <v>61.26643279999992</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1128914701492039</v>
+        <v>0.1143823917080751</v>
       </c>
       <c r="T56">
-        <v>1.344758615043291</v>
+        <v>1.374642139822031</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.05138188528586233</v>
+        <v>0.05044766918975573</v>
       </c>
       <c r="W56">
-        <v>0.1904825174345988</v>
+        <v>0.1906701080266971</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5138188528586232</v>
+        <v>0.5044766918975574</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1563406356833172</v>
+        <v>0.1776213651645002</v>
       </c>
       <c r="C57">
-        <v>-70.27016490108599</v>
+        <v>-233.5472501763429</v>
       </c>
       <c r="D57">
-        <v>1193.739835098914</v>
+        <v>1054.244749823657</v>
       </c>
       <c r="E57">
-        <v>1054.61</v>
+        <v>1078.392</v>
       </c>
       <c r="F57">
-        <v>1308.01</v>
+        <v>1331.792</v>
       </c>
       <c r="G57">
         <v>44</v>
@@ -5967,45 +5967,45 @@
         <v>132.5</v>
       </c>
       <c r="M57">
-        <v>262.6484080000001</v>
+        <v>314.0365536000001</v>
       </c>
       <c r="N57">
-        <v>-130.1484080000001</v>
+        <v>-181.5365536000001</v>
       </c>
       <c r="O57">
-        <v>-13.01484080000001</v>
+        <v>-18.15365536000001</v>
       </c>
       <c r="P57">
-        <v>-117.1335672000001</v>
+        <v>-163.3828982400001</v>
       </c>
       <c r="Q57">
-        <v>61.26643279999992</v>
+        <v>15.01710175999989</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1143823917080751</v>
+        <v>0.1162381948859472</v>
       </c>
       <c r="T57">
-        <v>1.374642139822031</v>
+        <v>1.411839227703967</v>
       </c>
       <c r="U57">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.05044766918975573</v>
+        <v>0.04219254048010287</v>
       </c>
       <c r="W57">
-        <v>0.1906701080266971</v>
+        <v>0.2258509989547917</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.5044766918975574</v>
+        <v>0.4219254048010287</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1776213651645002</v>
+        <v>0.1795213651645002</v>
       </c>
       <c r="C58">
-        <v>-233.5472501763429</v>
+        <v>-268.2147947919077</v>
       </c>
       <c r="D58">
-        <v>1054.244749823657</v>
+        <v>1043.359205208093</v>
       </c>
       <c r="E58">
-        <v>1078.392</v>
+        <v>1102.174</v>
       </c>
       <c r="F58">
-        <v>1331.792</v>
+        <v>1355.574</v>
       </c>
       <c r="G58">
         <v>44</v>
@@ -6049,37 +6049,37 @@
         <v>132.5</v>
       </c>
       <c r="M58">
-        <v>314.0365536000001</v>
+        <v>319.6443492000001</v>
       </c>
       <c r="N58">
-        <v>-181.5365536000001</v>
+        <v>-187.1443492000001</v>
       </c>
       <c r="O58">
-        <v>-18.15365536000001</v>
+        <v>-18.71443492000001</v>
       </c>
       <c r="P58">
-        <v>-163.3828982400001</v>
+        <v>-168.4299142800001</v>
       </c>
       <c r="Q58">
-        <v>15.01710175999989</v>
+        <v>9.970085719999901</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1162381948859472</v>
+        <v>0.1178762924414344</v>
       </c>
       <c r="T58">
-        <v>1.411839227703967</v>
+        <v>1.444672698115687</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.04219254048010287</v>
+        <v>0.04145232047168002</v>
       </c>
       <c r="W58">
-        <v>0.2258509989547917</v>
+        <v>0.2260255428327779</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4219254048010287</v>
+        <v>0.4145232047168002</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1795213651645002</v>
+        <v>0.1814213651645002</v>
       </c>
       <c r="C59">
-        <v>-268.2147947919077</v>
+        <v>-302.6598406536657</v>
       </c>
       <c r="D59">
-        <v>1043.359205208093</v>
+        <v>1032.696159346335</v>
       </c>
       <c r="E59">
-        <v>1102.174</v>
+        <v>1125.956</v>
       </c>
       <c r="F59">
-        <v>1355.574</v>
+        <v>1379.356</v>
       </c>
       <c r="G59">
         <v>44</v>
@@ -6131,37 +6131,37 @@
         <v>132.5</v>
       </c>
       <c r="M59">
-        <v>319.6443492000001</v>
+        <v>325.2521448000001</v>
       </c>
       <c r="N59">
-        <v>-187.1443492000001</v>
+        <v>-192.7521448000001</v>
       </c>
       <c r="O59">
-        <v>-18.71443492000001</v>
+        <v>-19.27521448000001</v>
       </c>
       <c r="P59">
-        <v>-168.4299142800001</v>
+        <v>-173.4769303200001</v>
       </c>
       <c r="Q59">
-        <v>9.970085719999901</v>
+        <v>4.923069679999941</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1178762924414344</v>
+        <v>0.1195923946424209</v>
       </c>
       <c r="T59">
-        <v>1.444672698115687</v>
+        <v>1.479069667118442</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.04145232047168002</v>
+        <v>0.04073762529113381</v>
       </c>
       <c r="W59">
-        <v>0.2260255428327779</v>
+        <v>0.2261940679563507</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.4145232047168002</v>
+        <v>0.4073762529113381</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1814213651645002</v>
+        <v>0.1833213651645001</v>
       </c>
       <c r="C60">
-        <v>-302.6598406536655</v>
+        <v>-336.8891405063907</v>
       </c>
       <c r="D60">
-        <v>1032.696159346335</v>
+        <v>1022.24885949361</v>
       </c>
       <c r="E60">
-        <v>1125.956</v>
+        <v>1149.738</v>
       </c>
       <c r="F60">
-        <v>1379.356</v>
+        <v>1403.138</v>
       </c>
       <c r="G60">
         <v>44</v>
@@ -6213,37 +6213,37 @@
         <v>132.5</v>
       </c>
       <c r="M60">
-        <v>325.2521448</v>
+        <v>330.8599404</v>
       </c>
       <c r="N60">
-        <v>-192.7521448</v>
+        <v>-198.3599404000001</v>
       </c>
       <c r="O60">
-        <v>-19.27521448</v>
+        <v>-19.83599404000001</v>
       </c>
       <c r="P60">
-        <v>-173.47693032</v>
+        <v>-178.5239463600001</v>
       </c>
       <c r="Q60">
-        <v>4.923069679999998</v>
+        <v>-0.1239463600000477</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1195923946424209</v>
+        <v>0.1213922091458945</v>
       </c>
       <c r="T60">
-        <v>1.479069667118441</v>
+        <v>1.515144537048159</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.04073762529113381</v>
+        <v>0.04004715706586036</v>
       </c>
       <c r="W60">
-        <v>0.2261940679563507</v>
+        <v>0.2263568803638701</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.4073762529113382</v>
+        <v>0.4004715706586035</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1833213651645001</v>
+        <v>0.1852213651645002</v>
       </c>
       <c r="C61">
-        <v>-336.8891405063907</v>
+        <v>-370.9091765742546</v>
       </c>
       <c r="D61">
-        <v>1022.24885949361</v>
+        <v>1012.010823425745</v>
       </c>
       <c r="E61">
-        <v>1149.738</v>
+        <v>1173.52</v>
       </c>
       <c r="F61">
-        <v>1403.138</v>
+        <v>1426.92</v>
       </c>
       <c r="G61">
         <v>44</v>
@@ -6295,37 +6295,37 @@
         <v>132.5</v>
       </c>
       <c r="M61">
-        <v>330.8599404</v>
+        <v>336.4677360000001</v>
       </c>
       <c r="N61">
-        <v>-198.3599404000001</v>
+        <v>-203.9677360000001</v>
       </c>
       <c r="O61">
-        <v>-19.83599404000001</v>
+        <v>-20.39677360000001</v>
       </c>
       <c r="P61">
-        <v>-178.5239463600001</v>
+        <v>-183.5709624000001</v>
       </c>
       <c r="Q61">
-        <v>-0.1239463600000477</v>
+        <v>-5.170962400000064</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1213922091458945</v>
+        <v>0.1232820143745419</v>
       </c>
       <c r="T61">
-        <v>1.515144537048159</v>
+        <v>1.553023150474363</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.04004715706586036</v>
+        <v>0.03937970444809602</v>
       </c>
       <c r="W61">
-        <v>0.2263568803638701</v>
+        <v>0.226514265691139</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4004715706586035</v>
+        <v>0.3937970444809601</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1852213651645002</v>
+        <v>0.1871213651645002</v>
       </c>
       <c r="C62">
-        <v>-370.9091765742546</v>
+        <v>-404.7261739731002</v>
       </c>
       <c r="D62">
-        <v>1012.010823425745</v>
+        <v>1001.9758260269</v>
       </c>
       <c r="E62">
-        <v>1173.52</v>
+        <v>1197.302</v>
       </c>
       <c r="F62">
-        <v>1426.92</v>
+        <v>1450.702</v>
       </c>
       <c r="G62">
         <v>44</v>
@@ -6377,37 +6377,37 @@
         <v>132.5</v>
       </c>
       <c r="M62">
-        <v>336.4677360000001</v>
+        <v>342.0755316000001</v>
       </c>
       <c r="N62">
-        <v>-203.9677360000001</v>
+        <v>-209.5755316000001</v>
       </c>
       <c r="O62">
-        <v>-20.39677360000001</v>
+        <v>-20.95755316000001</v>
       </c>
       <c r="P62">
-        <v>-183.5709624000001</v>
+        <v>-188.6179784400001</v>
       </c>
       <c r="Q62">
-        <v>-5.170962400000064</v>
+        <v>-10.21797844000011</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1232820143745419</v>
+        <v>0.1252687326918379</v>
       </c>
       <c r="T62">
-        <v>1.553023150474363</v>
+        <v>1.592844256896783</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.03937970444809602</v>
+        <v>0.03873413552271739</v>
       </c>
       <c r="W62">
-        <v>0.226514265691139</v>
+        <v>0.2266664908437432</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3937970444809601</v>
+        <v>0.3873413552271738</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1871213651645002</v>
+        <v>0.1890213651645002</v>
       </c>
       <c r="C63">
-        <v>-404.7261739731002</v>
+        <v>-438.3461133325834</v>
       </c>
       <c r="D63">
-        <v>1001.9758260269</v>
+        <v>992.1378866674166</v>
       </c>
       <c r="E63">
-        <v>1197.302</v>
+        <v>1221.084</v>
       </c>
       <c r="F63">
-        <v>1450.702</v>
+        <v>1474.484</v>
       </c>
       <c r="G63">
         <v>44</v>
@@ -6459,37 +6459,37 @@
         <v>132.5</v>
       </c>
       <c r="M63">
-        <v>342.0755316000001</v>
+        <v>347.6833272000001</v>
       </c>
       <c r="N63">
-        <v>-209.5755316000001</v>
+        <v>-215.1833272000001</v>
       </c>
       <c r="O63">
-        <v>-20.95755316000001</v>
+        <v>-21.51833272000001</v>
       </c>
       <c r="P63">
-        <v>-188.6179784400001</v>
+        <v>-193.6649944800001</v>
       </c>
       <c r="Q63">
-        <v>-10.21797844000011</v>
+        <v>-15.26499448000007</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1252687326918379</v>
+        <v>0.1273600151310968</v>
       </c>
       <c r="T63">
-        <v>1.592844256896783</v>
+        <v>1.634761211025646</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.03873413552271739</v>
+        <v>0.03810939140138324</v>
       </c>
       <c r="W63">
-        <v>0.2266664908437432</v>
+        <v>0.2268138055075538</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3873413552271738</v>
+        <v>0.3810939140138324</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1890213651645002</v>
+        <v>0.1909213651645001</v>
       </c>
       <c r="C64">
-        <v>-438.3461133325834</v>
+        <v>-471.7747426819606</v>
       </c>
       <c r="D64">
-        <v>992.1378866674166</v>
+        <v>982.4912573180396</v>
       </c>
       <c r="E64">
-        <v>1221.084</v>
+        <v>1244.866</v>
       </c>
       <c r="F64">
-        <v>1474.484</v>
+        <v>1498.266</v>
       </c>
       <c r="G64">
         <v>44</v>
@@ -6541,37 +6541,37 @@
         <v>132.5</v>
       </c>
       <c r="M64">
-        <v>347.6833272000001</v>
+        <v>353.2911228</v>
       </c>
       <c r="N64">
-        <v>-215.1833272000001</v>
+        <v>-220.7911228000001</v>
       </c>
       <c r="O64">
-        <v>-21.51833272000001</v>
+        <v>-22.07911228000001</v>
       </c>
       <c r="P64">
-        <v>-193.6649944800001</v>
+        <v>-198.7120105200001</v>
       </c>
       <c r="Q64">
-        <v>-15.26499448000007</v>
+        <v>-20.31201052000006</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1273600151310968</v>
+        <v>0.1295643398643697</v>
       </c>
       <c r="T64">
-        <v>1.634761211025646</v>
+        <v>1.678943946458771</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.03810939140138324</v>
+        <v>0.03750448042675811</v>
       </c>
       <c r="W64">
-        <v>0.2268138055075538</v>
+        <v>0.2269564435153704</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3810939140138324</v>
+        <v>0.3750448042675811</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1909213651645001</v>
+        <v>0.1928213651645002</v>
       </c>
       <c r="C65">
-        <v>-471.7747426819606</v>
+        <v>-505.0175886491506</v>
       </c>
       <c r="D65">
-        <v>982.4912573180396</v>
+        <v>973.0304113508496</v>
       </c>
       <c r="E65">
-        <v>1244.866</v>
+        <v>1268.648</v>
       </c>
       <c r="F65">
-        <v>1498.266</v>
+        <v>1522.048</v>
       </c>
       <c r="G65">
         <v>44</v>
@@ -6623,37 +6623,37 @@
         <v>132.5</v>
       </c>
       <c r="M65">
-        <v>353.2911228</v>
+        <v>358.8989184000001</v>
       </c>
       <c r="N65">
-        <v>-220.7911228000001</v>
+        <v>-226.3989184000001</v>
       </c>
       <c r="O65">
-        <v>-22.07911228000001</v>
+        <v>-22.63989184000001</v>
       </c>
       <c r="P65">
-        <v>-198.7120105200001</v>
+        <v>-203.7590265600001</v>
       </c>
       <c r="Q65">
-        <v>-20.31201052000006</v>
+        <v>-25.35902656000007</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1295643398643697</v>
+        <v>0.1318911270828244</v>
       </c>
       <c r="T65">
-        <v>1.678943946458771</v>
+        <v>1.725581278304848</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.03750448042675811</v>
+        <v>0.03691847292009001</v>
       </c>
       <c r="W65">
-        <v>0.2269564435153704</v>
+        <v>0.2270946240854428</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3750448042675811</v>
+        <v>0.3691847292009001</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1928213651645002</v>
+        <v>0.1947213651645002</v>
       </c>
       <c r="C66">
-        <v>-505.0175886491506</v>
+        <v>-538.0799670189263</v>
       </c>
       <c r="D66">
-        <v>973.0304113508496</v>
+        <v>963.7500329810739</v>
       </c>
       <c r="E66">
-        <v>1268.648</v>
+        <v>1292.43</v>
       </c>
       <c r="F66">
-        <v>1522.048</v>
+        <v>1545.83</v>
       </c>
       <c r="G66">
         <v>44</v>
@@ -6705,37 +6705,37 @@
         <v>132.5</v>
       </c>
       <c r="M66">
-        <v>358.8989184000001</v>
+        <v>364.506714</v>
       </c>
       <c r="N66">
-        <v>-226.3989184000001</v>
+        <v>-232.0067140000001</v>
       </c>
       <c r="O66">
-        <v>-22.63989184000001</v>
+        <v>-23.20067140000001</v>
       </c>
       <c r="P66">
-        <v>-203.7590265600001</v>
+        <v>-208.8060426000001</v>
       </c>
       <c r="Q66">
-        <v>-25.35902656000007</v>
+        <v>-30.40604260000006</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1318911270828244</v>
+        <v>0.1343508735709051</v>
       </c>
       <c r="T66">
-        <v>1.725581278304848</v>
+        <v>1.77488360054213</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.03691847292009001</v>
+        <v>0.03635049641362709</v>
       </c>
       <c r="W66">
-        <v>0.2270946240854428</v>
+        <v>0.2272285529456667</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3691847292009001</v>
+        <v>0.3635049641362709</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1947213651645002</v>
+        <v>0.1966213651645002</v>
       </c>
       <c r="C67">
-        <v>-538.0799670189263</v>
+        <v>-570.9669926926156</v>
       </c>
       <c r="D67">
-        <v>963.7500329810739</v>
+        <v>954.6450073073847</v>
       </c>
       <c r="E67">
-        <v>1292.43</v>
+        <v>1316.212</v>
       </c>
       <c r="F67">
-        <v>1545.83</v>
+        <v>1569.612</v>
       </c>
       <c r="G67">
         <v>44</v>
@@ -6787,37 +6787,37 @@
         <v>132.5</v>
       </c>
       <c r="M67">
-        <v>364.506714</v>
+        <v>370.1145096000001</v>
       </c>
       <c r="N67">
-        <v>-232.0067140000001</v>
+        <v>-237.6145096000001</v>
       </c>
       <c r="O67">
-        <v>-23.20067140000001</v>
+        <v>-23.76145096000001</v>
       </c>
       <c r="P67">
-        <v>-208.8060426000001</v>
+        <v>-213.8530586400001</v>
       </c>
       <c r="Q67">
-        <v>-30.40604260000006</v>
+        <v>-35.45305864000008</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1343508735709051</v>
+        <v>0.1369553110288729</v>
       </c>
       <c r="T67">
-        <v>1.77488360054213</v>
+        <v>1.827086059381604</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.03635049641362709</v>
+        <v>0.03579973131645092</v>
       </c>
       <c r="W67">
-        <v>0.2272285529456667</v>
+        <v>0.2273584233555809</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3635049641362709</v>
+        <v>0.3579973131645092</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1966213651645002</v>
+        <v>0.1985213651645002</v>
       </c>
       <c r="C68">
-        <v>-570.9669926926156</v>
+        <v>-603.6835890885186</v>
       </c>
       <c r="D68">
-        <v>954.6450073073847</v>
+        <v>945.7104109114816</v>
       </c>
       <c r="E68">
-        <v>1316.212</v>
+        <v>1339.994</v>
       </c>
       <c r="F68">
-        <v>1569.612</v>
+        <v>1593.394</v>
       </c>
       <c r="G68">
         <v>44</v>
@@ -6869,37 +6869,37 @@
         <v>132.5</v>
       </c>
       <c r="M68">
-        <v>370.1145096000001</v>
+        <v>375.7223052000001</v>
       </c>
       <c r="N68">
-        <v>-237.6145096000001</v>
+        <v>-243.2223052000001</v>
       </c>
       <c r="O68">
-        <v>-23.76145096000001</v>
+        <v>-24.32223052000001</v>
       </c>
       <c r="P68">
-        <v>-213.8530586400001</v>
+        <v>-218.9000746800001</v>
       </c>
       <c r="Q68">
-        <v>-35.45305864000008</v>
+        <v>-40.50007468000007</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1369553110288729</v>
+        <v>0.139717593181263</v>
       </c>
       <c r="T68">
-        <v>1.827086059381604</v>
+        <v>1.882452303605289</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.03579973131645092</v>
+        <v>0.03526540696844419</v>
       </c>
       <c r="W68">
-        <v>0.2273584233555809</v>
+        <v>0.2274844170368409</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3579973131645092</v>
+        <v>0.3526540696844419</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1985213651645002</v>
+        <v>0.2004213651645002</v>
       </c>
       <c r="C69">
-        <v>-603.6835890885186</v>
+        <v>-636.2344970193467</v>
       </c>
       <c r="D69">
-        <v>945.7104109114816</v>
+        <v>936.9415029806537</v>
       </c>
       <c r="E69">
-        <v>1339.994</v>
+        <v>1363.776</v>
       </c>
       <c r="F69">
-        <v>1593.394</v>
+        <v>1617.176</v>
       </c>
       <c r="G69">
         <v>44</v>
@@ -6951,37 +6951,37 @@
         <v>132.5</v>
       </c>
       <c r="M69">
-        <v>375.7223052000001</v>
+        <v>381.3301008000001</v>
       </c>
       <c r="N69">
-        <v>-243.2223052000001</v>
+        <v>-248.8301008000001</v>
       </c>
       <c r="O69">
-        <v>-24.32223052000001</v>
+        <v>-24.88301008000001</v>
       </c>
       <c r="P69">
-        <v>-218.9000746800001</v>
+        <v>-223.9470907200001</v>
       </c>
       <c r="Q69">
-        <v>-40.50007468000007</v>
+        <v>-45.54709072000009</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.139717593181263</v>
+        <v>0.1426525179681774</v>
       </c>
       <c r="T69">
-        <v>1.882452303605289</v>
+        <v>1.941278938092955</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.03526540696844419</v>
+        <v>0.03474679804243765</v>
       </c>
       <c r="W69">
-        <v>0.2274844170368409</v>
+        <v>0.2276067050215932</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3526540696844419</v>
+        <v>0.3474679804243765</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2004213651645002</v>
+        <v>0.2023213651645002</v>
       </c>
       <c r="C70">
-        <v>-636.2344970193467</v>
+        <v>-668.6242830803103</v>
       </c>
       <c r="D70">
-        <v>936.9415029806537</v>
+        <v>928.33371691969</v>
       </c>
       <c r="E70">
-        <v>1363.776</v>
+        <v>1387.558</v>
       </c>
       <c r="F70">
-        <v>1617.176</v>
+        <v>1640.958</v>
       </c>
       <c r="G70">
         <v>44</v>
@@ -7033,37 +7033,37 @@
         <v>132.5</v>
       </c>
       <c r="M70">
-        <v>381.3301008000001</v>
+        <v>386.9378964000001</v>
       </c>
       <c r="N70">
-        <v>-248.8301008000001</v>
+        <v>-254.4378964000001</v>
       </c>
       <c r="O70">
-        <v>-24.88301008000001</v>
+        <v>-25.44378964000002</v>
       </c>
       <c r="P70">
-        <v>-223.9470907200001</v>
+        <v>-228.9941067600001</v>
       </c>
       <c r="Q70">
-        <v>-45.54709072000009</v>
+        <v>-50.59410676000013</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1426525179681774</v>
+        <v>0.1457767927413444</v>
       </c>
       <c r="T70">
-        <v>1.941278938092955</v>
+        <v>2.00390083932176</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.03474679804243765</v>
+        <v>0.03424322125921392</v>
       </c>
       <c r="W70">
-        <v>0.2276067050215932</v>
+        <v>0.2277254484270774</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3474679804243765</v>
+        <v>0.3424322125921392</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2023213651645002</v>
+        <v>0.2042213651645002</v>
       </c>
       <c r="C71">
-        <v>-668.6242830803103</v>
+        <v>-700.8573475790452</v>
       </c>
       <c r="D71">
-        <v>928.33371691969</v>
+        <v>919.8826524209551</v>
       </c>
       <c r="E71">
-        <v>1387.558</v>
+        <v>1411.34</v>
       </c>
       <c r="F71">
-        <v>1640.958</v>
+        <v>1664.74</v>
       </c>
       <c r="G71">
         <v>44</v>
@@ -7115,37 +7115,37 @@
         <v>132.5</v>
       </c>
       <c r="M71">
-        <v>386.9378964000001</v>
+        <v>392.5456920000001</v>
       </c>
       <c r="N71">
-        <v>-254.4378964000001</v>
+        <v>-260.0456920000001</v>
       </c>
       <c r="O71">
-        <v>-25.44378964000002</v>
+        <v>-26.00456920000002</v>
       </c>
       <c r="P71">
-        <v>-228.9941067600001</v>
+        <v>-234.0411228000001</v>
       </c>
       <c r="Q71">
-        <v>-50.59410676000013</v>
+        <v>-55.64112280000012</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1457767927413444</v>
+        <v>0.1491093524993893</v>
       </c>
       <c r="T71">
-        <v>2.00390083932176</v>
+        <v>2.070697533965819</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03424322125921392</v>
+        <v>0.0337540323840823</v>
       </c>
       <c r="W71">
-        <v>0.2277254484270774</v>
+        <v>0.2278407991638334</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3424322125921392</v>
+        <v>0.3375403238408229</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2042213651645002</v>
+        <v>0.2061213651645002</v>
       </c>
       <c r="C72">
-        <v>-700.8573475790452</v>
+        <v>-732.9379320363061</v>
       </c>
       <c r="D72">
-        <v>919.8826524209551</v>
+        <v>911.5840679636943</v>
       </c>
       <c r="E72">
-        <v>1411.34</v>
+        <v>1435.122</v>
       </c>
       <c r="F72">
-        <v>1664.74</v>
+        <v>1688.522</v>
       </c>
       <c r="G72">
         <v>44</v>
@@ -7197,37 +7197,37 @@
         <v>132.5</v>
       </c>
       <c r="M72">
-        <v>392.5456920000001</v>
+        <v>398.1534876000001</v>
       </c>
       <c r="N72">
-        <v>-260.0456920000001</v>
+        <v>-265.6534876000002</v>
       </c>
       <c r="O72">
-        <v>-26.00456920000002</v>
+        <v>-26.56534876000002</v>
       </c>
       <c r="P72">
-        <v>-234.0411228000001</v>
+        <v>-239.0881388400002</v>
       </c>
       <c r="Q72">
-        <v>-55.64112280000012</v>
+        <v>-60.68813884000016</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1491093524993893</v>
+        <v>0.1526717439648854</v>
       </c>
       <c r="T72">
-        <v>2.070697533965819</v>
+        <v>2.142100897206019</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.0337540323840823</v>
+        <v>0.03327862347726423</v>
       </c>
       <c r="W72">
-        <v>0.2278407991638334</v>
+        <v>0.2279529005840611</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3375403238408229</v>
+        <v>0.3327862347726422</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2061213651645002</v>
+        <v>0.2080213651645001</v>
       </c>
       <c r="C73">
-        <v>-732.9379320363055</v>
+        <v>-764.8701262842874</v>
       </c>
       <c r="D73">
-        <v>911.5840679636947</v>
+        <v>903.4338737157127</v>
       </c>
       <c r="E73">
-        <v>1435.122</v>
+        <v>1458.904</v>
       </c>
       <c r="F73">
-        <v>1688.522</v>
+        <v>1712.304</v>
       </c>
       <c r="G73">
         <v>44</v>
@@ -7279,37 +7279,37 @@
         <v>132.5</v>
       </c>
       <c r="M73">
-        <v>398.1534876000001</v>
+        <v>403.7612832</v>
       </c>
       <c r="N73">
-        <v>-265.6534876000001</v>
+        <v>-271.2612832000001</v>
       </c>
       <c r="O73">
-        <v>-26.56534876000001</v>
+        <v>-27.12612832000001</v>
       </c>
       <c r="P73">
-        <v>-239.0881388400001</v>
+        <v>-244.1351548800001</v>
       </c>
       <c r="Q73">
-        <v>-60.68813884000005</v>
+        <v>-65.73515488000007</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1526717439648854</v>
+        <v>0.1564885919636313</v>
       </c>
       <c r="T73">
-        <v>2.142100897206018</v>
+        <v>2.218604500677662</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03327862347726424</v>
+        <v>0.03281642037341335</v>
       </c>
       <c r="W73">
-        <v>0.2279529005840611</v>
+        <v>0.2280618880759491</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3327862347726425</v>
+        <v>0.3281642037341334</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2080213651645001</v>
+        <v>0.2099213651645001</v>
       </c>
       <c r="C74">
-        <v>-764.8701262842874</v>
+        <v>-796.6578751875456</v>
       </c>
       <c r="D74">
-        <v>903.4338737157127</v>
+        <v>895.4281248124546</v>
       </c>
       <c r="E74">
-        <v>1458.904</v>
+        <v>1482.686</v>
       </c>
       <c r="F74">
-        <v>1712.304</v>
+        <v>1736.086</v>
       </c>
       <c r="G74">
         <v>44</v>
@@ -7361,37 +7361,37 @@
         <v>132.5</v>
       </c>
       <c r="M74">
-        <v>403.7612832</v>
+        <v>409.3690788000001</v>
       </c>
       <c r="N74">
-        <v>-271.2612832000001</v>
+        <v>-276.8690788000001</v>
       </c>
       <c r="O74">
-        <v>-27.12612832000001</v>
+        <v>-27.68690788000001</v>
       </c>
       <c r="P74">
-        <v>-244.1351548800001</v>
+        <v>-249.1821709200001</v>
       </c>
       <c r="Q74">
-        <v>-65.73515488000007</v>
+        <v>-70.78217092000011</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1564885919636313</v>
+        <v>0.1605881694437658</v>
       </c>
       <c r="T74">
-        <v>2.218604500677662</v>
+        <v>2.300775037739797</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03281642037341335</v>
+        <v>0.03236688036829809</v>
       </c>
       <c r="W74">
-        <v>0.2280618880759491</v>
+        <v>0.2281678896091553</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3281642037341334</v>
+        <v>0.3236688036829809</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2099213651645001</v>
+        <v>0.2118213651645002</v>
       </c>
       <c r="C75">
-        <v>-796.6578751875456</v>
+        <v>-828.3049850097028</v>
       </c>
       <c r="D75">
-        <v>895.4281248124546</v>
+        <v>887.5630149902973</v>
       </c>
       <c r="E75">
-        <v>1482.686</v>
+        <v>1506.468</v>
       </c>
       <c r="F75">
-        <v>1736.086</v>
+        <v>1759.868</v>
       </c>
       <c r="G75">
         <v>44</v>
@@ -7443,37 +7443,37 @@
         <v>132.5</v>
       </c>
       <c r="M75">
-        <v>409.3690788000001</v>
+        <v>414.9768744</v>
       </c>
       <c r="N75">
-        <v>-276.8690788000001</v>
+        <v>-282.4768744</v>
       </c>
       <c r="O75">
-        <v>-27.68690788000001</v>
+        <v>-28.24768744000001</v>
       </c>
       <c r="P75">
-        <v>-249.1821709200001</v>
+        <v>-254.22918696</v>
       </c>
       <c r="Q75">
-        <v>-70.78217092000011</v>
+        <v>-75.82918696000004</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1605881694437658</v>
+        <v>0.1650030990377568</v>
       </c>
       <c r="T75">
-        <v>2.300775037739797</v>
+        <v>2.389266385345175</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03236688036829809</v>
+        <v>0.03192949009305082</v>
       </c>
       <c r="W75">
-        <v>0.2281678896091553</v>
+        <v>0.2282710262360586</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3236688036829809</v>
+        <v>0.3192949009305083</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2118213651645002</v>
+        <v>0.2137213651645001</v>
       </c>
       <c r="C76">
-        <v>-828.3049850097028</v>
+        <v>-859.8151294475466</v>
       </c>
       <c r="D76">
-        <v>887.5630149902973</v>
+        <v>879.8348705524535</v>
       </c>
       <c r="E76">
-        <v>1506.468</v>
+        <v>1530.25</v>
       </c>
       <c r="F76">
-        <v>1759.868</v>
+        <v>1783.65</v>
       </c>
       <c r="G76">
         <v>44</v>
@@ -7525,37 +7525,37 @@
         <v>132.5</v>
       </c>
       <c r="M76">
-        <v>414.9768744</v>
+        <v>420.58467</v>
       </c>
       <c r="N76">
-        <v>-282.4768744</v>
+        <v>-288.0846700000001</v>
       </c>
       <c r="O76">
-        <v>-28.24768744000001</v>
+        <v>-28.80846700000001</v>
       </c>
       <c r="P76">
-        <v>-254.22918696</v>
+        <v>-259.2762030000001</v>
       </c>
       <c r="Q76">
-        <v>-75.82918696000004</v>
+        <v>-80.87620300000006</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1650030990377568</v>
+        <v>0.1697712229992671</v>
       </c>
       <c r="T76">
-        <v>2.389266385345175</v>
+        <v>2.484837040758982</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03192949009305082</v>
+        <v>0.03150376355847682</v>
       </c>
       <c r="W76">
-        <v>0.2282710262360586</v>
+        <v>0.2283714125529112</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3192949009305083</v>
+        <v>0.315037635584768</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2137213651645001</v>
+        <v>0.2156213651645002</v>
       </c>
       <c r="C77">
-        <v>-859.8151294475466</v>
+        <v>-891.1918553526083</v>
       </c>
       <c r="D77">
-        <v>879.8348705524535</v>
+        <v>872.240144647392</v>
       </c>
       <c r="E77">
-        <v>1530.25</v>
+        <v>1554.032</v>
       </c>
       <c r="F77">
-        <v>1783.65</v>
+        <v>1807.432</v>
       </c>
       <c r="G77">
         <v>44</v>
@@ -7607,37 +7607,37 @@
         <v>132.5</v>
       </c>
       <c r="M77">
-        <v>420.58467</v>
+        <v>426.1924656</v>
       </c>
       <c r="N77">
-        <v>-288.0846700000001</v>
+        <v>-293.6924656000001</v>
       </c>
       <c r="O77">
-        <v>-28.80846700000001</v>
+        <v>-29.36924656000001</v>
       </c>
       <c r="P77">
-        <v>-259.2762030000001</v>
+        <v>-264.3232190400001</v>
       </c>
       <c r="Q77">
-        <v>-80.87620300000006</v>
+        <v>-85.92321904000008</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1697712229992671</v>
+        <v>0.1749366906242366</v>
       </c>
       <c r="T77">
-        <v>2.484837040758982</v>
+        <v>2.588371917457273</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03150376355847682</v>
+        <v>0.03108924035376001</v>
       </c>
       <c r="W77">
-        <v>0.2283714125529112</v>
+        <v>0.2284691571245834</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.315037635584768</v>
+        <v>0.3108924035376001</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2156213651645002</v>
+        <v>0.2175213651645002</v>
       </c>
       <c r="C78">
-        <v>-891.1918553526083</v>
+        <v>-922.4385881589417</v>
       </c>
       <c r="D78">
-        <v>872.240144647392</v>
+        <v>864.7754118410585</v>
       </c>
       <c r="E78">
-        <v>1554.032</v>
+        <v>1577.814</v>
       </c>
       <c r="F78">
-        <v>1807.432</v>
+        <v>1831.214</v>
       </c>
       <c r="G78">
         <v>44</v>
@@ -7689,37 +7689,37 @@
         <v>132.5</v>
       </c>
       <c r="M78">
-        <v>426.1924656</v>
+        <v>431.8002612000001</v>
       </c>
       <c r="N78">
-        <v>-293.6924656000001</v>
+        <v>-299.3002612000001</v>
       </c>
       <c r="O78">
-        <v>-29.36924656000001</v>
+        <v>-29.93002612000002</v>
       </c>
       <c r="P78">
-        <v>-264.3232190400001</v>
+        <v>-269.3702350800001</v>
       </c>
       <c r="Q78">
-        <v>-85.92321904000008</v>
+        <v>-90.97023508000009</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1749366906242366</v>
+        <v>0.1805513293470295</v>
       </c>
       <c r="T78">
-        <v>2.588371917457273</v>
+        <v>2.700909826911937</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03108924035376001</v>
+        <v>0.03068548398552936</v>
       </c>
       <c r="W78">
-        <v>0.2284691571245834</v>
+        <v>0.2285643628762122</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3108924035376001</v>
+        <v>0.3068548398552935</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2175213651645002</v>
+        <v>0.2194213651645002</v>
       </c>
       <c r="C79">
-        <v>-922.4385881589417</v>
+        <v>-953.5586370345663</v>
       </c>
       <c r="D79">
-        <v>864.7754118410585</v>
+        <v>857.437362965434</v>
       </c>
       <c r="E79">
-        <v>1577.814</v>
+        <v>1601.596</v>
       </c>
       <c r="F79">
-        <v>1831.214</v>
+        <v>1854.996</v>
       </c>
       <c r="G79">
         <v>44</v>
@@ -7771,37 +7771,37 @@
         <v>132.5</v>
       </c>
       <c r="M79">
-        <v>431.8002612000001</v>
+        <v>437.4080568000001</v>
       </c>
       <c r="N79">
-        <v>-299.3002612000001</v>
+        <v>-304.9080568000002</v>
       </c>
       <c r="O79">
-        <v>-29.93002612000002</v>
+        <v>-30.49080568000002</v>
       </c>
       <c r="P79">
-        <v>-269.3702350800001</v>
+        <v>-274.4172511200002</v>
       </c>
       <c r="Q79">
-        <v>-90.97023508000009</v>
+        <v>-96.01725112000017</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1805513293470295</v>
+        <v>0.1866763897718945</v>
       </c>
       <c r="T79">
-        <v>2.700909826911937</v>
+        <v>2.823678455407934</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03068548398552936</v>
+        <v>0.03029208034468924</v>
       </c>
       <c r="W79">
-        <v>0.2285643628762122</v>
+        <v>0.2286571274547223</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3068548398552935</v>
+        <v>0.3029208034468923</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2194213651645002</v>
+        <v>0.2213213651645002</v>
       </c>
       <c r="C80">
-        <v>-953.5586370345663</v>
+        <v>-984.5551997728325</v>
       </c>
       <c r="D80">
-        <v>857.437362965434</v>
+        <v>850.2228002271678</v>
       </c>
       <c r="E80">
-        <v>1601.596</v>
+        <v>1625.378</v>
       </c>
       <c r="F80">
-        <v>1854.996</v>
+        <v>1878.778</v>
       </c>
       <c r="G80">
         <v>44</v>
@@ -7853,37 +7853,37 @@
         <v>132.5</v>
       </c>
       <c r="M80">
-        <v>437.4080568000001</v>
+        <v>443.0158524000001</v>
       </c>
       <c r="N80">
-        <v>-304.9080568000002</v>
+        <v>-310.5158524000001</v>
       </c>
       <c r="O80">
-        <v>-30.49080568000002</v>
+        <v>-31.05158524000001</v>
       </c>
       <c r="P80">
-        <v>-274.4172511200002</v>
+        <v>-279.4642671600001</v>
       </c>
       <c r="Q80">
-        <v>-96.01725112000017</v>
+        <v>-101.0642671600001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1866763897718945</v>
+        <v>0.1933847892848418</v>
       </c>
       <c r="T80">
-        <v>2.823678455407934</v>
+        <v>2.958139334236884</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03029208034468924</v>
+        <v>0.02990863628969317</v>
       </c>
       <c r="W80">
-        <v>0.2286571274547223</v>
+        <v>0.2287475435628903</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3029208034468923</v>
+        <v>0.2990863628969318</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2213213651645002</v>
+        <v>0.2232213651645002</v>
       </c>
       <c r="C81">
-        <v>-984.5551997728325</v>
+        <v>-1015.431367438915</v>
       </c>
       <c r="D81">
-        <v>850.2228002271678</v>
+        <v>843.1286325610849</v>
       </c>
       <c r="E81">
-        <v>1625.378</v>
+        <v>1649.16</v>
       </c>
       <c r="F81">
-        <v>1878.778</v>
+        <v>1902.56</v>
       </c>
       <c r="G81">
         <v>44</v>
@@ -7935,37 +7935,37 @@
         <v>132.5</v>
       </c>
       <c r="M81">
-        <v>443.0158524000001</v>
+        <v>448.6236480000001</v>
       </c>
       <c r="N81">
-        <v>-310.5158524000001</v>
+        <v>-316.1236480000001</v>
       </c>
       <c r="O81">
-        <v>-31.05158524000001</v>
+        <v>-31.61236480000001</v>
       </c>
       <c r="P81">
-        <v>-279.4642671600001</v>
+        <v>-284.5112832000001</v>
       </c>
       <c r="Q81">
-        <v>-101.0642671600001</v>
+        <v>-106.1112832000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1933847892848418</v>
+        <v>0.2007640287490839</v>
       </c>
       <c r="T81">
-        <v>2.958139334236884</v>
+        <v>3.106046300948728</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02990863628969317</v>
+        <v>0.02953477833607201</v>
       </c>
       <c r="W81">
-        <v>0.2287475435628903</v>
+        <v>0.2288356992683542</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2990863628969318</v>
+        <v>0.2953477833607201</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2232213651645002</v>
+        <v>0.2251213651645002</v>
       </c>
       <c r="C82">
-        <v>-1015.431367438915</v>
+        <v>-1046.19012878561</v>
       </c>
       <c r="D82">
-        <v>843.1286325610849</v>
+        <v>836.15187121439</v>
       </c>
       <c r="E82">
-        <v>1649.16</v>
+        <v>1672.942</v>
       </c>
       <c r="F82">
-        <v>1902.56</v>
+        <v>1926.342</v>
       </c>
       <c r="G82">
         <v>44</v>
@@ -8017,37 +8017,37 @@
         <v>132.5</v>
       </c>
       <c r="M82">
-        <v>448.6236480000001</v>
+        <v>454.2314436000001</v>
       </c>
       <c r="N82">
-        <v>-316.1236480000001</v>
+        <v>-321.7314436000001</v>
       </c>
       <c r="O82">
-        <v>-31.61236480000001</v>
+        <v>-32.17314436000002</v>
       </c>
       <c r="P82">
-        <v>-284.5112832000001</v>
+        <v>-289.5582992400001</v>
       </c>
       <c r="Q82">
-        <v>-106.1112832000001</v>
+        <v>-111.1582992400001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2007640287490839</v>
+        <v>0.2089200302621936</v>
       </c>
       <c r="T82">
-        <v>3.106046300948728</v>
+        <v>3.269522422051293</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02953477833607201</v>
+        <v>0.02917015144303408</v>
       </c>
       <c r="W82">
-        <v>0.2288356992683542</v>
+        <v>0.2289216782897326</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2953477833607201</v>
+        <v>0.2917015144303408</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2251213651645002</v>
+        <v>0.2270213651645002</v>
       </c>
       <c r="C83">
-        <v>-1046.19012878561</v>
+        <v>-1076.834374451691</v>
       </c>
       <c r="D83">
-        <v>836.15187121439</v>
+        <v>829.2896255483098</v>
       </c>
       <c r="E83">
-        <v>1672.942</v>
+        <v>1696.724</v>
       </c>
       <c r="F83">
-        <v>1926.342</v>
+        <v>1950.124</v>
       </c>
       <c r="G83">
         <v>44</v>
@@ -8099,37 +8099,37 @@
         <v>132.5</v>
       </c>
       <c r="M83">
-        <v>454.2314436000001</v>
+        <v>459.8392392000001</v>
       </c>
       <c r="N83">
-        <v>-321.7314436000001</v>
+        <v>-327.3392392000002</v>
       </c>
       <c r="O83">
-        <v>-32.17314436000002</v>
+        <v>-32.73392392000002</v>
       </c>
       <c r="P83">
-        <v>-289.5582992400001</v>
+        <v>-294.6053152800002</v>
       </c>
       <c r="Q83">
-        <v>-111.1582992400001</v>
+        <v>-116.2053152800002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2089200302621936</v>
+        <v>0.2179822541656488</v>
       </c>
       <c r="T83">
-        <v>3.269522422051293</v>
+        <v>3.451162556609698</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02917015144303408</v>
+        <v>0.02881441788885074</v>
       </c>
       <c r="W83">
-        <v>0.2289216782897326</v>
+        <v>0.229005560261809</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2917015144303408</v>
+        <v>0.2881441788885073</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2270213651645002</v>
+        <v>0.2289213651645002</v>
       </c>
       <c r="C84">
-        <v>-1076.834374451691</v>
+        <v>-1107.366900955212</v>
       </c>
       <c r="D84">
-        <v>829.2896255483098</v>
+        <v>822.5390990447885</v>
       </c>
       <c r="E84">
-        <v>1696.724</v>
+        <v>1720.506</v>
       </c>
       <c r="F84">
-        <v>1950.124</v>
+        <v>1973.906</v>
       </c>
       <c r="G84">
         <v>44</v>
@@ -8181,37 +8181,37 @@
         <v>132.5</v>
       </c>
       <c r="M84">
-        <v>459.8392392000001</v>
+        <v>465.4470348000001</v>
       </c>
       <c r="N84">
-        <v>-327.3392392000002</v>
+        <v>-332.9470348000001</v>
       </c>
       <c r="O84">
-        <v>-32.73392392000002</v>
+        <v>-33.29470348000001</v>
       </c>
       <c r="P84">
-        <v>-294.6053152800002</v>
+        <v>-299.6523313200001</v>
       </c>
       <c r="Q84">
-        <v>-116.2053152800002</v>
+        <v>-121.2523313200001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2179822541656488</v>
+        <v>0.2281106220577458</v>
       </c>
       <c r="T84">
-        <v>3.451162556609698</v>
+        <v>3.65417211876321</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02881441788885074</v>
+        <v>0.02846725622753929</v>
       </c>
       <c r="W84">
-        <v>0.229005560261809</v>
+        <v>0.2290874209815462</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2881441788885073</v>
+        <v>0.2846725622753929</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2289213651645002</v>
+        <v>0.2308213651645002</v>
       </c>
       <c r="C85">
-        <v>-1107.366900955212</v>
+        <v>-1137.790414493356</v>
       </c>
       <c r="D85">
-        <v>822.5390990447885</v>
+        <v>815.8975855066443</v>
       </c>
       <c r="E85">
-        <v>1720.506</v>
+        <v>1744.288</v>
       </c>
       <c r="F85">
-        <v>1973.906</v>
+        <v>1997.688</v>
       </c>
       <c r="G85">
         <v>44</v>
@@ -8263,37 +8263,37 @@
         <v>132.5</v>
       </c>
       <c r="M85">
-        <v>465.4470348000001</v>
+        <v>471.0548304000001</v>
       </c>
       <c r="N85">
-        <v>-332.9470348000001</v>
+        <v>-338.5548304000001</v>
       </c>
       <c r="O85">
-        <v>-33.29470348000001</v>
+        <v>-33.85548304000002</v>
       </c>
       <c r="P85">
-        <v>-299.6523313200001</v>
+        <v>-304.6993473600001</v>
       </c>
       <c r="Q85">
-        <v>-121.2523313200001</v>
+        <v>-126.2993473600001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2281106220577458</v>
+        <v>0.239505035936355</v>
       </c>
       <c r="T85">
-        <v>3.65417211876321</v>
+        <v>3.882557876185911</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02846725622753929</v>
+        <v>0.02812836032006858</v>
       </c>
       <c r="W85">
-        <v>0.2290874209815462</v>
+        <v>0.2291673326365278</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2846725622753929</v>
+        <v>0.2812836032006858</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2308213651645001</v>
+        <v>0.2327213651645001</v>
       </c>
       <c r="C86">
-        <v>-1137.790414493355</v>
+        <v>-1168.10753455966</v>
       </c>
       <c r="D86">
-        <v>815.8975855066448</v>
+        <v>809.36246544034</v>
       </c>
       <c r="E86">
-        <v>1744.288</v>
+        <v>1768.07</v>
       </c>
       <c r="F86">
-        <v>1997.688</v>
+        <v>2021.47</v>
       </c>
       <c r="G86">
         <v>44</v>
@@ -8345,37 +8345,37 @@
         <v>132.5</v>
       </c>
       <c r="M86">
-        <v>471.0548304000001</v>
+        <v>476.6626260000001</v>
       </c>
       <c r="N86">
-        <v>-338.5548304000001</v>
+        <v>-344.1626260000002</v>
       </c>
       <c r="O86">
-        <v>-33.85548304000002</v>
+        <v>-34.41626260000002</v>
       </c>
       <c r="P86">
-        <v>-304.6993473600001</v>
+        <v>-309.7463634000001</v>
       </c>
       <c r="Q86">
-        <v>-126.2993473600001</v>
+        <v>-131.3463634000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2395050359363548</v>
+        <v>0.2524187049987784</v>
       </c>
       <c r="T86">
-        <v>3.882557876185909</v>
+        <v>4.141395067931636</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02812836032006858</v>
+        <v>0.02779743843395013</v>
       </c>
       <c r="W86">
-        <v>0.2291673326365278</v>
+        <v>0.2292453640172746</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2812836032006858</v>
+        <v>0.2779743843395012</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2327213651645001</v>
+        <v>0.2346213651645002</v>
       </c>
       <c r="C87">
-        <v>-1168.10753455966</v>
+        <v>-1198.320797388791</v>
       </c>
       <c r="D87">
-        <v>809.36246544034</v>
+        <v>802.931202611209</v>
       </c>
       <c r="E87">
-        <v>1768.07</v>
+        <v>1791.852</v>
       </c>
       <c r="F87">
-        <v>2021.47</v>
+        <v>2045.252</v>
       </c>
       <c r="G87">
         <v>44</v>
@@ -8427,37 +8427,37 @@
         <v>132.5</v>
       </c>
       <c r="M87">
-        <v>476.6626260000001</v>
+        <v>482.2704216000001</v>
       </c>
       <c r="N87">
-        <v>-344.1626260000002</v>
+        <v>-349.7704216000001</v>
       </c>
       <c r="O87">
-        <v>-34.41626260000002</v>
+        <v>-34.97704216000001</v>
       </c>
       <c r="P87">
-        <v>-309.7463634000001</v>
+        <v>-314.7933794400001</v>
       </c>
       <c r="Q87">
-        <v>-131.3463634000001</v>
+        <v>-136.3933794400001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2524187049987784</v>
+        <v>0.2671771839272626</v>
       </c>
       <c r="T87">
-        <v>4.141395067931636</v>
+        <v>4.437209001355324</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02779743843395013</v>
+        <v>0.02747421240564838</v>
       </c>
       <c r="W87">
-        <v>0.2292453640172746</v>
+        <v>0.2293215807147481</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2779743843395012</v>
+        <v>0.2747421240564839</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2346213651645002</v>
+        <v>0.2365213651645001</v>
       </c>
       <c r="C88">
-        <v>-1198.320797388791</v>
+        <v>-1228.432659238376</v>
       </c>
       <c r="D88">
-        <v>802.931202611209</v>
+        <v>796.6013407616244</v>
       </c>
       <c r="E88">
-        <v>1791.852</v>
+        <v>1815.634</v>
       </c>
       <c r="F88">
-        <v>2045.252</v>
+        <v>2069.034</v>
       </c>
       <c r="G88">
         <v>44</v>
@@ -8509,37 +8509,37 @@
         <v>132.5</v>
       </c>
       <c r="M88">
-        <v>482.2704216000001</v>
+        <v>487.8782172000001</v>
       </c>
       <c r="N88">
-        <v>-349.7704216000001</v>
+        <v>-355.3782172000001</v>
       </c>
       <c r="O88">
-        <v>-34.97704216000001</v>
+        <v>-35.53782172000001</v>
       </c>
       <c r="P88">
-        <v>-314.7933794400001</v>
+        <v>-319.8403954800001</v>
       </c>
       <c r="Q88">
-        <v>-136.3933794400001</v>
+        <v>-141.4403954800001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2671771839272626</v>
+        <v>0.2842061980755136</v>
       </c>
       <c r="T88">
-        <v>4.437209001355324</v>
+        <v>4.778532770690348</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02747421240564838</v>
+        <v>0.02715841686075587</v>
       </c>
       <c r="W88">
-        <v>0.2293215807147481</v>
+        <v>0.2293960453042338</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2747421240564839</v>
+        <v>0.2715841686075586</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2365213651645001</v>
+        <v>0.2384213651645002</v>
       </c>
       <c r="C89">
-        <v>-1228.432659238376</v>
+        <v>-1258.445499516814</v>
       </c>
       <c r="D89">
-        <v>796.6013407616244</v>
+        <v>790.3705004831858</v>
       </c>
       <c r="E89">
-        <v>1815.634</v>
+        <v>1839.416</v>
       </c>
       <c r="F89">
-        <v>2069.034</v>
+        <v>2092.816</v>
       </c>
       <c r="G89">
         <v>44</v>
@@ -8591,37 +8591,37 @@
         <v>132.5</v>
       </c>
       <c r="M89">
-        <v>487.8782172000001</v>
+        <v>493.4860128000001</v>
       </c>
       <c r="N89">
-        <v>-355.3782172000001</v>
+        <v>-360.9860128000001</v>
       </c>
       <c r="O89">
-        <v>-35.53782172000001</v>
+        <v>-36.09860128000002</v>
       </c>
       <c r="P89">
-        <v>-319.8403954800001</v>
+        <v>-324.8874115200001</v>
       </c>
       <c r="Q89">
-        <v>-141.4403954800001</v>
+        <v>-146.4874115200001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2842061980755136</v>
+        <v>0.3040733812484732</v>
       </c>
       <c r="T89">
-        <v>4.778532770690348</v>
+        <v>5.176743834914546</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02715841686075587</v>
+        <v>0.02684979848733819</v>
       </c>
       <c r="W89">
-        <v>0.2293960453042338</v>
+        <v>0.2294688175166857</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2715841686075586</v>
+        <v>0.2684979848733818</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2384213651645002</v>
+        <v>0.2403213651645001</v>
       </c>
       <c r="C90">
-        <v>-1258.445499516814</v>
+        <v>-1288.361623765447</v>
       </c>
       <c r="D90">
-        <v>790.3705004831858</v>
+        <v>784.2363762345531</v>
       </c>
       <c r="E90">
-        <v>1839.416</v>
+        <v>1863.198</v>
       </c>
       <c r="F90">
-        <v>2092.816</v>
+        <v>2116.598</v>
       </c>
       <c r="G90">
         <v>44</v>
@@ -8673,37 +8673,37 @@
         <v>132.5</v>
       </c>
       <c r="M90">
-        <v>493.4860128000001</v>
+        <v>499.0938084000001</v>
       </c>
       <c r="N90">
-        <v>-360.9860128000001</v>
+        <v>-366.5938084000002</v>
       </c>
       <c r="O90">
-        <v>-36.09860128000002</v>
+        <v>-36.65938084000002</v>
       </c>
       <c r="P90">
-        <v>-324.8874115200001</v>
+        <v>-329.9344275600001</v>
       </c>
       <c r="Q90">
-        <v>-146.4874115200001</v>
+        <v>-151.5344275600001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3040733812484732</v>
+        <v>0.3275527795437889</v>
       </c>
       <c r="T90">
-        <v>5.176743834914546</v>
+        <v>5.647356910815868</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02684979848733819</v>
+        <v>0.02654811535826697</v>
       </c>
       <c r="W90">
-        <v>0.2294688175166857</v>
+        <v>0.2295399543985207</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2684979848733818</v>
+        <v>0.2654811535826697</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2403213651645001</v>
+        <v>0.2422213651645002</v>
       </c>
       <c r="C91">
-        <v>-1288.361623765447</v>
+        <v>-1318.183266502914</v>
       </c>
       <c r="D91">
-        <v>784.2363762345531</v>
+        <v>778.1967334970861</v>
       </c>
       <c r="E91">
-        <v>1863.198</v>
+        <v>1886.98</v>
       </c>
       <c r="F91">
-        <v>2116.598</v>
+        <v>2140.38</v>
       </c>
       <c r="G91">
         <v>44</v>
@@ -8755,37 +8755,37 @@
         <v>132.5</v>
       </c>
       <c r="M91">
-        <v>499.0938084000001</v>
+        <v>504.701604</v>
       </c>
       <c r="N91">
-        <v>-366.5938084000002</v>
+        <v>-372.2016040000001</v>
       </c>
       <c r="O91">
-        <v>-36.65938084000002</v>
+        <v>-37.22016040000001</v>
       </c>
       <c r="P91">
-        <v>-329.9344275600001</v>
+        <v>-334.9814436000001</v>
       </c>
       <c r="Q91">
-        <v>-151.5344275600001</v>
+        <v>-156.5814436000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3275527795437889</v>
+        <v>0.3557280574981678</v>
       </c>
       <c r="T91">
-        <v>5.647356910815868</v>
+        <v>6.212092601897456</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02654811535826697</v>
+        <v>0.02625313629873068</v>
       </c>
       <c r="W91">
-        <v>0.2295399543985207</v>
+        <v>0.2296095104607593</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2654811535826697</v>
+        <v>0.2625313629873067</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2422213651645002</v>
+        <v>0.2441213651645001</v>
       </c>
       <c r="C92">
-        <v>-1318.183266502914</v>
+        <v>-1347.912593939092</v>
       </c>
       <c r="D92">
-        <v>778.1967334970861</v>
+        <v>772.2494060609079</v>
       </c>
       <c r="E92">
-        <v>1886.98</v>
+        <v>1910.762</v>
       </c>
       <c r="F92">
-        <v>2140.38</v>
+        <v>2164.162</v>
       </c>
       <c r="G92">
         <v>44</v>
@@ -8837,37 +8837,37 @@
         <v>132.5</v>
       </c>
       <c r="M92">
-        <v>504.701604</v>
+        <v>510.3093996000001</v>
       </c>
       <c r="N92">
-        <v>-372.2016040000001</v>
+        <v>-377.8093996000001</v>
       </c>
       <c r="O92">
-        <v>-37.22016040000001</v>
+        <v>-37.78093996000001</v>
       </c>
       <c r="P92">
-        <v>-334.9814436000001</v>
+        <v>-340.0284596400001</v>
       </c>
       <c r="Q92">
-        <v>-156.5814436000001</v>
+        <v>-161.6284596400001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3557280574981678</v>
+        <v>0.3901645083312976</v>
       </c>
       <c r="T92">
-        <v>6.212092601897456</v>
+        <v>6.902325113219395</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02625313629873068</v>
+        <v>0.02596464029544792</v>
       </c>
       <c r="W92">
-        <v>0.2296095104607593</v>
+        <v>0.2296775378183334</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2625313629873067</v>
+        <v>0.2596464029544792</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2441213651645001</v>
+        <v>0.2460213651645002</v>
       </c>
       <c r="C93">
-        <v>-1347.912593939092</v>
+        <v>-1377.551706565531</v>
       </c>
       <c r="D93">
-        <v>772.2494060609079</v>
+        <v>766.3922934344698</v>
       </c>
       <c r="E93">
-        <v>1910.762</v>
+        <v>1934.544</v>
       </c>
       <c r="F93">
-        <v>2164.162</v>
+        <v>2187.944</v>
       </c>
       <c r="G93">
         <v>44</v>
@@ -8919,37 +8919,37 @@
         <v>132.5</v>
       </c>
       <c r="M93">
-        <v>510.3093996000001</v>
+        <v>515.9171952000002</v>
       </c>
       <c r="N93">
-        <v>-377.8093996000001</v>
+        <v>-383.4171952000002</v>
       </c>
       <c r="O93">
-        <v>-37.78093996000001</v>
+        <v>-38.34171952000002</v>
       </c>
       <c r="P93">
-        <v>-340.0284596400001</v>
+        <v>-345.0754756800001</v>
       </c>
       <c r="Q93">
-        <v>-161.6284596400001</v>
+        <v>-166.6754756800001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3901645083312976</v>
+        <v>0.4332100718727099</v>
       </c>
       <c r="T93">
-        <v>6.902325113219395</v>
+        <v>7.765115752371822</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02596464029544792</v>
+        <v>0.02568241594441044</v>
       </c>
       <c r="W93">
-        <v>0.2296775378183334</v>
+        <v>0.229744086320308</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2596464029544792</v>
+        <v>0.2568241594441044</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2460213651645002</v>
+        <v>0.2479213651645002</v>
       </c>
       <c r="C94">
-        <v>-1377.551706565531</v>
+        <v>-1407.102641628885</v>
       </c>
       <c r="D94">
-        <v>766.3922934344698</v>
+        <v>760.623358371116</v>
       </c>
       <c r="E94">
-        <v>1934.544</v>
+        <v>1958.326</v>
       </c>
       <c r="F94">
-        <v>2187.944</v>
+        <v>2211.726000000001</v>
       </c>
       <c r="G94">
         <v>44</v>
@@ -9001,37 +9001,37 @@
         <v>132.5</v>
       </c>
       <c r="M94">
-        <v>515.9171952000002</v>
+        <v>521.5249908000002</v>
       </c>
       <c r="N94">
-        <v>-383.4171952000002</v>
+        <v>-389.0249908000002</v>
       </c>
       <c r="O94">
-        <v>-38.34171952000002</v>
+        <v>-38.90249908000002</v>
       </c>
       <c r="P94">
-        <v>-345.0754756800001</v>
+        <v>-350.1224917200001</v>
       </c>
       <c r="Q94">
-        <v>-166.6754756800001</v>
+        <v>-171.7224917200001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4332100718727099</v>
+        <v>0.4885543678545257</v>
       </c>
       <c r="T94">
-        <v>7.765115752371822</v>
+        <v>8.874418002710655</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02568241594441044</v>
+        <v>0.02540626093425549</v>
       </c>
       <c r="W94">
-        <v>0.229744086320308</v>
+        <v>0.2298092036717026</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2568241594441044</v>
+        <v>0.254062609342555</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2479213651645002</v>
+        <v>0.2498213651645002</v>
       </c>
       <c r="C95">
-        <v>-1407.102641628885</v>
+        <v>-1436.567375493481</v>
       </c>
       <c r="D95">
-        <v>760.623358371116</v>
+        <v>754.9406245065193</v>
       </c>
       <c r="E95">
-        <v>1958.326</v>
+        <v>1982.108</v>
       </c>
       <c r="F95">
-        <v>2211.726000000001</v>
+        <v>2235.508</v>
       </c>
       <c r="G95">
         <v>44</v>
@@ -9083,37 +9083,37 @@
         <v>132.5</v>
       </c>
       <c r="M95">
-        <v>521.5249908000002</v>
+        <v>527.1327864000001</v>
       </c>
       <c r="N95">
-        <v>-389.0249908000002</v>
+        <v>-394.6327864000001</v>
       </c>
       <c r="O95">
-        <v>-38.90249908000002</v>
+        <v>-39.46327864000001</v>
       </c>
       <c r="P95">
-        <v>-350.1224917200001</v>
+        <v>-355.1695077600001</v>
       </c>
       <c r="Q95">
-        <v>-171.7224917200001</v>
+        <v>-176.7695077600001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4885543678545257</v>
+        <v>0.5623467624969467</v>
       </c>
       <c r="T95">
-        <v>8.874418002710655</v>
+        <v>10.3534876698291</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02540626093425549</v>
+        <v>0.02513598156261447</v>
       </c>
       <c r="W95">
-        <v>0.2298092036717026</v>
+        <v>0.2298729355475355</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.254062609342555</v>
+        <v>0.2513598156261448</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2498213651645002</v>
+        <v>0.2517213651645002</v>
       </c>
       <c r="C96">
-        <v>-1436.567375493481</v>
+        <v>-1465.947825898757</v>
       </c>
       <c r="D96">
-        <v>754.9406245065193</v>
+        <v>749.3421741012432</v>
       </c>
       <c r="E96">
-        <v>1982.108</v>
+        <v>2005.89</v>
       </c>
       <c r="F96">
-        <v>2235.508</v>
+        <v>2259.29</v>
       </c>
       <c r="G96">
         <v>44</v>
@@ -9165,37 +9165,37 @@
         <v>132.5</v>
       </c>
       <c r="M96">
-        <v>527.1327864000001</v>
+        <v>532.7405820000001</v>
       </c>
       <c r="N96">
-        <v>-394.6327864000001</v>
+        <v>-400.2405820000001</v>
       </c>
       <c r="O96">
-        <v>-39.46327864000001</v>
+        <v>-40.02405820000001</v>
       </c>
       <c r="P96">
-        <v>-355.1695077600001</v>
+        <v>-360.2165238000001</v>
       </c>
       <c r="Q96">
-        <v>-176.7695077600001</v>
+        <v>-181.8165238000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5623467624969467</v>
+        <v>0.6656561149963361</v>
       </c>
       <c r="T96">
-        <v>10.3534876698291</v>
+        <v>12.42418520379492</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02513598156261447</v>
+        <v>0.02487139228300801</v>
       </c>
       <c r="W96">
-        <v>0.2298729355475355</v>
+        <v>0.2299353256996667</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2513598156261448</v>
+        <v>0.2487139228300801</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2517213651645002</v>
+        <v>0.2536213651645002</v>
       </c>
       <c r="C97">
-        <v>-1465.947825898757</v>
+        <v>-1495.245854116998</v>
       </c>
       <c r="D97">
-        <v>749.3421741012432</v>
+        <v>743.8261458830029</v>
       </c>
       <c r="E97">
-        <v>2005.89</v>
+        <v>2029.672</v>
       </c>
       <c r="F97">
-        <v>2259.29</v>
+        <v>2283.072000000001</v>
       </c>
       <c r="G97">
         <v>44</v>
@@ -9247,37 +9247,37 @@
         <v>132.5</v>
       </c>
       <c r="M97">
-        <v>532.7405820000001</v>
+        <v>538.3483776000002</v>
       </c>
       <c r="N97">
-        <v>-400.2405820000001</v>
+        <v>-405.8483776000002</v>
       </c>
       <c r="O97">
-        <v>-40.02405820000001</v>
+        <v>-40.58483776000002</v>
       </c>
       <c r="P97">
-        <v>-360.2165238000001</v>
+        <v>-365.2635398400001</v>
       </c>
       <c r="Q97">
-        <v>-181.8165238000001</v>
+        <v>-186.8635398400001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6656561149963361</v>
+        <v>0.8206201437454206</v>
       </c>
       <c r="T97">
-        <v>12.42418520379492</v>
+        <v>15.53023150474366</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02487139228300801</v>
+        <v>0.02461231528006001</v>
       </c>
       <c r="W97">
-        <v>0.2299353256996667</v>
+        <v>0.2299964160569619</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2487139228300801</v>
+        <v>0.2461231528006002</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2536213651645001</v>
+        <v>0.2555213651645001</v>
       </c>
       <c r="C98">
-        <v>-1495.245854116997</v>
+        <v>-1524.463267016464</v>
       </c>
       <c r="D98">
-        <v>743.8261458830029</v>
+        <v>738.3907329835359</v>
       </c>
       <c r="E98">
-        <v>2029.672</v>
+        <v>2053.454</v>
       </c>
       <c r="F98">
-        <v>2283.072</v>
+        <v>2306.854</v>
       </c>
       <c r="G98">
         <v>44</v>
@@ -9329,37 +9329,37 @@
         <v>132.5</v>
       </c>
       <c r="M98">
-        <v>538.3483776</v>
+        <v>543.9561732000001</v>
       </c>
       <c r="N98">
-        <v>-405.8483776</v>
+        <v>-411.4561732000001</v>
       </c>
       <c r="O98">
-        <v>-40.58483776000001</v>
+        <v>-41.14561732000001</v>
       </c>
       <c r="P98">
-        <v>-365.26353984</v>
+        <v>-370.31055588</v>
       </c>
       <c r="Q98">
-        <v>-186.86353984</v>
+        <v>-191.91055588</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8206201437454186</v>
+        <v>1.078893524993892</v>
       </c>
       <c r="T98">
-        <v>15.53023150474362</v>
+        <v>20.70697533965816</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02461231528006001</v>
+        <v>0.02435858007098722</v>
       </c>
       <c r="W98">
-        <v>0.2299964160569619</v>
+        <v>0.2300562468192612</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2461231528006002</v>
+        <v>0.2435858007098723</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2555213651645001</v>
+        <v>0.2574213651645002</v>
       </c>
       <c r="C99">
-        <v>-1524.463267016464</v>
+        <v>-1553.60181903473</v>
       </c>
       <c r="D99">
-        <v>738.3907329835359</v>
+        <v>733.0341809652699</v>
       </c>
       <c r="E99">
-        <v>2053.454</v>
+        <v>2077.236</v>
       </c>
       <c r="F99">
-        <v>2306.854</v>
+        <v>2330.636</v>
       </c>
       <c r="G99">
         <v>44</v>
@@ -9411,37 +9411,37 @@
         <v>132.5</v>
       </c>
       <c r="M99">
-        <v>543.9561732000001</v>
+        <v>549.5639688000001</v>
       </c>
       <c r="N99">
-        <v>-411.4561732000001</v>
+        <v>-417.0639688000001</v>
       </c>
       <c r="O99">
-        <v>-41.14561732000001</v>
+        <v>-41.70639688000001</v>
       </c>
       <c r="P99">
-        <v>-370.31055588</v>
+        <v>-375.3575719200001</v>
       </c>
       <c r="Q99">
-        <v>-191.91055588</v>
+        <v>-196.9575719200001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.078893524993892</v>
+        <v>1.595440287490837</v>
       </c>
       <c r="T99">
-        <v>20.70697533965816</v>
+        <v>31.06046300948724</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02435858007098722</v>
+        <v>0.02411002313148736</v>
       </c>
       <c r="W99">
-        <v>0.2300562468192612</v>
+        <v>0.2301148565455953</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2435858007098723</v>
+        <v>0.2411002313148736</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2574213651645002</v>
+        <v>0.2593213651645002</v>
       </c>
       <c r="C100">
-        <v>-1553.60181903473</v>
+        <v>-1582.663214066738</v>
       </c>
       <c r="D100">
-        <v>733.0341809652699</v>
+        <v>727.7547859332624</v>
       </c>
       <c r="E100">
-        <v>2077.236</v>
+        <v>2101.018</v>
       </c>
       <c r="F100">
-        <v>2330.636</v>
+        <v>2354.418</v>
       </c>
       <c r="G100">
         <v>44</v>
@@ -9493,37 +9493,37 @@
         <v>132.5</v>
       </c>
       <c r="M100">
-        <v>549.5639688000001</v>
+        <v>555.1717644</v>
       </c>
       <c r="N100">
-        <v>-417.0639688000001</v>
+        <v>-422.6717644</v>
       </c>
       <c r="O100">
-        <v>-41.70639688000001</v>
+        <v>-42.26717644000001</v>
       </c>
       <c r="P100">
-        <v>-375.3575719200001</v>
+        <v>-380.40458796</v>
       </c>
       <c r="Q100">
-        <v>-196.9575719200001</v>
+        <v>-202.00458796</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.595440287490837</v>
+        <v>3.145080574981674</v>
       </c>
       <c r="T100">
-        <v>31.06046300948724</v>
+        <v>62.12092601897449</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02411002313148736</v>
+        <v>0.02386648754430062</v>
       </c>
       <c r="W100">
-        <v>0.2301148565455953</v>
+        <v>0.2301722822370539</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2411002313148736</v>
+        <v>0.2386648754430062</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2593213651645002</v>
-      </c>
-      <c r="C101">
-        <v>-1582.663214066738</v>
-      </c>
-      <c r="D101">
-        <v>727.7547859332624</v>
-      </c>
-      <c r="E101">
-        <v>2101.018</v>
-      </c>
-      <c r="F101">
-        <v>2354.418</v>
-      </c>
-      <c r="G101">
-        <v>44</v>
-      </c>
-      <c r="H101">
-        <v>2124.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>310.9</v>
-      </c>
-      <c r="K101">
-        <v>178.4</v>
-      </c>
-      <c r="L101">
-        <v>132.5</v>
-      </c>
-      <c r="M101">
-        <v>555.1717644</v>
-      </c>
-      <c r="N101">
-        <v>-422.6717644</v>
-      </c>
-      <c r="O101">
-        <v>-42.26717644000001</v>
-      </c>
-      <c r="P101">
-        <v>-380.40458796</v>
-      </c>
-      <c r="Q101">
-        <v>-202.00458796</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.145080574981674</v>
-      </c>
-      <c r="T101">
-        <v>62.12092601897449</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02386648754430062</v>
-      </c>
-      <c r="W101">
-        <v>0.2301722822370539</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2386648754430062</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
